--- a/grants.xlsx
+++ b/grants.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I84"/>
+  <dimension ref="A1:J82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -437,52 +425,58 @@
     <col width="80" customWidth="1" min="7" max="7"/>
     <col width="80" customWidth="1" min="8" max="8"/>
     <col width="76" customWidth="1" min="9" max="9"/>
+    <col width="80" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>summary</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>donor</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>geographic_location</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>deadline</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>view_grant</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>application_link</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>grant_page_url</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>source_listing_url</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>ai_summary</t>
         </is>
       </c>
     </row>
@@ -532,6 +526,11 @@
           <t>https://www2.fundsforngos.org/tag/lebanon/</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>The OIF offers grants to support the writing and co-production of French-language creative works in book publishing, live performance, and cinema-audiovisual.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -579,6 +578,11 @@
           <t>https://www2.fundsforngos.org/tag/lebanon/</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>This grant enables Canadian artists and arts organizations to present, promote, and share their artistic work across Canada and internationally.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -622,6 +626,11 @@
           <t>https://www2.fundsforngos.org/tag/lebanon/</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>This grant opportunity offers global writers, poets, translators, and visual artists an inclusive platform to submit original works, fostering cultural exchange, creativity, and global visibility.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -669,27 +678,36 @@
           <t>https://www2.fundsforngos.org/tag/lebanon/</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>This global media contest aims to engage contributors worldwide in documenting diverse folk culture through submitted photographs, audio, and video.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>International Travel Fund for Market Development in Australia</t>
+          <t>Monthly Creative Challenge: Design Something Massive</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Deadline: 14-Apr-2026 The International Travel Fund supports Australian artists, authors, illustrators, creative workers, and organizations to attend key international market development platforms and events. Grants help cover travel, accommodation, visas, and professional expenses, enabling participants to build global networks, partnerships, and exposure. Funding is offered in fixed amounts of $5,000, $10,000, $15,000, or $20,000, targeting</t>
+          <t>Deadline: 24-Mar-2026 The Monthly Creative Challenge invites creators worldwide to explore scale and impact by designing massive structures, creatures, or environments that dominate their surroundings. Participants from any creative field—illustration, 3D art, animation, game design, architecture, motion graphics, web, or digital fashion—can submit original work for recognition and prizes, including a one-year Adobe Creative Cloud</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Creative Australia</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>The Rookies</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>creators worldwide</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>14-Apr-2026</t>
+          <t>24-Mar-2026</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -699,44 +717,49 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://creative.gov.au/investments-opportunities/international-travel-fund-market-development</t>
+          <t>https://www.therookies.co/contests/groups/monthly-art-challenge-colossal</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/arts-culture/international-travel-fund-for-market-development-in-australia/</t>
+          <t>https://www2.fundsforngos.org/arts-culture/monthly-creative-challenge-design-something-massive/</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>https://www2.fundsforngos.org/tag/lebanon/</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>This monthly creative challenge invites professional creators worldwide to design massive structures, creatures, or environments that explore scale and impact.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Monthly Creative Challenge: Design Something Massive</t>
+          <t>PRS Foundation announces Composers Fund (United Kingdom)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Deadline: 24-Mar-2026 The Monthly Creative Challenge invites creators worldwide to explore scale and impact by designing massive structures, creatures, or environments that dominate their surroundings. Participants from any creative field—illustration, 3D art, animation, game design, architecture, motion graphics, web, or digital fashion—can submit original work for recognition and prizes, including a one-year Adobe Creative Cloud</t>
+          <t>Deadline: 31-Mar-2026 The PRS Foundation Composers’ Fund provides £8,000–£15,000 to UK-based composers at pivotal stages in their careers. Funding supports activities such as recordings, performances, residencies, international collaborations, and promotional work, enabling composers to achieve significant artistic and professional growth. Overview of the Fund The Composers’ Fund offers targeted financial support to composers demonstrating potential</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>The Rookies</t>
+          <t>PRS Foundation</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>creators worldwide</t>
+          <t>Grants range between</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>24-Mar-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -746,17 +769,22 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.therookies.co/contests/groups/monthly-art-challenge-colossal</t>
+          <t>https://prsfoundation.com/funding-support/funding-music-creators/next-steps/the-composers-fund/</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/arts-culture/monthly-creative-challenge-design-something-massive/</t>
+          <t>https://www2.fundsforngos.org/arts-culture/prs-foundation-announces-composers-fund-united-kingdom/</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>https://www2.fundsforngos.org/tag/lebanon/</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>The PRS Foundation Composers' Fund provides financial support to UK-based composers at pivotal career stages to enable significant artistic and professional growth.</t>
         </is>
       </c>
     </row>
@@ -806,31 +834,28 @@
           <t>https://www2.fundsforngos.org/tag/lebanon/</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Tibetan Arts and Culture Fund 2026 (India)</t>
+          <t>Apply Now: Starter Company Plus Program (Canada)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Deadline: 30-Apr-2026 The Tibetan Arts and Culture Fund (TACF-2026) by the Central Tibetan Administration provides grants of ₹1,00,000 to ₹3,00,000 to support projects preserving and promoting Tibetan arts and culture. Open to individual artists, researchers, and organizations, the fund supports both traditional and contemporary cultural initiatives. Applicants must submit a proposal, budget, and references, with</t>
+          <t>Deadline: 01-May-2026 The Starter Company Plus Program supports adults in Ontario who want to start, grow, or buy a small business. Eligible participants receive training, coaching, mentoring, networking support, and may apply for a financial award of up to $5,000 after successfully completing the program. About the Program The Starter Company Plus Program helps aspiring</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CTA</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>individual artists, researchers, and organizations, the fund supports both traditional and contemporary cultural initiatives. Applicants must submit a proposal, budget, and references, with final selection through a review and interview process.</t>
-        </is>
-      </c>
+          <t>Town of Orangeville</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>01-May-2026</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -840,12 +865,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://tibet.net/tibetan-arts-and-culture-fund-tacf-2026/</t>
+          <t>https://www.orangeville.ca/en/economic-development/starter-company.aspx</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/arts-culture/tibetan-arts-and-culture-fund-2026-india/</t>
+          <t>https://www2.fundsforngos.org/business-industry/apply-now-starter-company-plus-program-canada/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -853,31 +878,28 @@
           <t>https://www2.fundsforngos.org/tag/lebanon/</t>
         </is>
       </c>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Translation Funding for Australian Literary Works</t>
+          <t>Bangkok Business Challenge 2026: Compete for Global Startup Glory</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Deadline: 14-Apr-2026 The Creative Australia Translation Fund provides financial support for translating literary works, enabling international publishers to translate Australian creative works and Australian publishers to translate non-English works into English. The fund prioritizes creative writing, narrative non-fiction, and playwriting, supporting global access and cultural exchange. Grants range from AUD $5,000 to $10,000, mainly covering</t>
+          <t>Deadline: 15-Mar-2026 The Bangkok Business Challenge 2026 invites undergraduate and postgraduate students worldwide to present innovative, investor-ready startup ideas. Participants compete for a total prize pool of USD 42,900, royal trophies, and global recognition through business plan submissions, live pitches, and venture exhibits. What is the Bangkok Business Challenge 2026? The Bangkok Business Challenge 2026</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Creative Australia</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>to the Translation Fund?</t>
-        </is>
-      </c>
+          <t>Sasin School of Management</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>14-Apr-2026</t>
+          <t>15-Mar-2026</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -887,12 +909,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://creative.gov.au/investments-opportunities/translation-fund-literature</t>
+          <t>https://bbc.sasin.edu/2026</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/arts-culture/translation-funding-for-australian-literary-works/</t>
+          <t>https://www2.fundsforngos.org/business-industry/bangkok-business-challenge-2026-compete-for-global-startup-glory/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -900,27 +922,32 @@
           <t>https://www2.fundsforngos.org/tag/lebanon/</t>
         </is>
       </c>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Bangkok Business Challenge 2026: Compete for Global Startup Glory</t>
+          <t>Abdul Hameed Shoman Award for Children’s Literature</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Deadline: 15-Mar-2026 The Bangkok Business Challenge 2026 invites undergraduate and postgraduate students worldwide to present innovative, investor-ready startup ideas. Participants compete for a total prize pool of USD 42,900, royal trophies, and global recognition through business plan submissions, live pitches, and venture exhibits. What is the Bangkok Business Challenge 2026? The Bangkok Business Challenge 2026</t>
+          <t>Deadline: 31-Mar-2026 The Abdul Hameed Shoman Foundation invites Arab writers to submit original Arabic literary works for children aged 6–8, focusing on early school experiences such as embarrassment and bullying. Winners receive publication, prize money, and recognition, promoting high-quality children’s literature that supports imagination, emotional development, and cultural identity. Overview The award encourages the creation</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sasin School of Management</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Abdul Hameed Shoman Foundation</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Prepare your manuscript</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>15-Mar-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -930,12 +957,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://bbc.sasin.edu/2026</t>
+          <t>https://shoman.org/en/ChildrenLiteratureAward</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/business-industry/bangkok-business-challenge-2026-compete-for-global-startup-glory/</t>
+          <t>https://www2.fundsforngos.org/children/abdul-hameed-shoman-award-for-childrens-literature/</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -943,27 +970,28 @@
           <t>https://www2.fundsforngos.org/tag/lebanon/</t>
         </is>
       </c>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>UNEP Invites Proposals for National Textile LCI Database Development (India)</t>
+          <t>CFAs: Educate A Child Multi-Country Initiative (Denmark)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Deadline: 05-Apr-2026 The United Nations Environment Programme has launched a call for proposals to develop a National Textile Life Cycle Inventory (LCI) Database for India under the InTex Programme. The initiative aims to enable a circular textile economy by improving access to reliable environmental data across the textile value chain. Eligible applicants must be not-for-profit</t>
+          <t>Deadline: 14-Apr-2026 UNHCR is inviting qualified partners to support a multi-country Monitoring, Evaluation, and Learning (MEL) partnership under the Educate A Child (EAC) programme. With a budget of up to USD 1,000,000 over four years, the initiative aims to improve access to quality primary education for refugee children across Chad, Kenya, Pakistan, Uganda, and Syria.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>UNEP</t>
+          <t>UN Partner Portal</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>05-Apr-2026</t>
+          <t>14-Apr-2026</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -973,12 +1001,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.unep.org/calls-for-proposals</t>
+          <t>https://www.unpartnerportal.org/landing/opportunities/</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/business-industry/unep-invites-proposals-for-national-textile-lci-database-development-india/</t>
+          <t>https://www2.fundsforngos.org/children/cfas-educate-a-child-multi-country-initiative-denmark/</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -986,31 +1014,28 @@
           <t>https://www2.fundsforngos.org/tag/lebanon/</t>
         </is>
       </c>
+      <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Abdul Hameed Shoman Award for Children’s Literature</t>
+          <t>Healthy Lungs for Life Grants Programme 2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Deadline: 31-Mar-2026 The Abdul Hameed Shoman Foundation invites Arab writers to submit original Arabic literary works for children aged 6–8, focusing on early school experiences such as embarrassment and bullying. Winners receive publication, prize money, and recognition, promoting high-quality children’s literature that supports imagination, emotional development, and cultural identity. Overview The award encourages the creation</t>
+          <t>Deadline: 16-Apr-2026 The Healthy Lungs for Life Grants Programme 2026 provides funding to support initiatives that raise awareness, educate communities, and promote lung health across all age groups. Grants range from €1,000 to €5,000, enabling not-for-profits, healthcare professionals, and community groups to organize impactful projects that focus on prevention, early intervention, and healthy habits. Overview</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Abdul Hameed Shoman Foundation</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Prepare your manuscript</t>
-        </is>
-      </c>
+          <t>European Lung Foundation</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>31-Mar-2026</t>
+          <t>16-Apr-2026</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1020,12 +1045,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://shoman.org/en/ChildrenLiteratureAward</t>
+          <t>https://europeanlung.org/en/projects-and-campaigns/healthy-lungs-for-life/hold-your-own-event/apply-for-a-grant/</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/children/abdul-hameed-shoman-award-for-childrens-literature/</t>
+          <t>https://www2.fundsforngos.org/children/healthy-lungs-for-life-grants-programme-2026/</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1033,27 +1058,32 @@
           <t>https://www2.fundsforngos.org/tag/lebanon/</t>
         </is>
       </c>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Healthy Lungs for Life Grants Programme 2026</t>
+          <t>RFPs: Breakthrough Innovations to Reduce the Cost of Severe Malnutrition Treatment</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Deadline: 16-Apr-2026 The Healthy Lungs for Life Grants Programme 2026 provides funding to support initiatives that raise awareness, educate communities, and promote lung health across all age groups. Grants range from €1,000 to €5,000, enabling not-for-profits, healthcare professionals, and community groups to organize impactful projects that focus on prevention, early intervention, and healthy habits. Overview</t>
+          <t>Deadline: 28-Apr-2026 The Gates Foundation is seeking breakthrough innovations that can reduce the total cost of treating Severe Acute Malnutrition (SAM) while maintaining quality, safety, and successful treatment outcomes for children in Sub-Saharan Africa and South Asia. The call supports system-level solutions that can achieve at least a 20% to 30% reduction in cost per</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>European Lung Foundation</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Gates Foundation</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>a broad range of organizations with strong technical and implementation</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>28-Apr-2026</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1063,12 +1093,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://europeanlung.org/en/projects-and-campaigns/healthy-lungs-for-life/hold-your-own-event/apply-for-a-grant/</t>
+          <t>https://gcgh.grandchallenges.org/challenge/breakthrough-innovations-significantly-reduce-cost-severe-acute-malnutrition-treatment</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/children/healthy-lungs-for-life-grants-programme-2026/</t>
+          <t>https://www2.fundsforngos.org/children/rfps-breakthrough-innovations-to-reduce-the-cost-of-severe-malnutrition-treatment/</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1076,31 +1106,28 @@
           <t>https://www2.fundsforngos.org/tag/lebanon/</t>
         </is>
       </c>
+      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>“25 to 25: Young and Bold” Competition (Ukraine)</t>
+          <t>Call for EOIs: Climate Services and Community SATs (Honduras)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Deadline: 30-Mar-2026 The “25 to 25: Young and Bold” Competition by the Media Development Foundation celebrates young media professionals under 25 who are actively contributing to independent media and community engagement. The program recognizes emerging talent, encourages professional growth, and supports meaningful contributions in journalism, editing, media management, communications, and photography. Nominations are open to</t>
+          <t>Deadline: 26-Mar-2026 The World Food Programme (WFP) is seeking partners to enhance climate information services and community early warning systems for small-scale farmers in Honduras. The initiative focuses on co-produced climate alerts, institutional capacity building, and community preparedness to improve livelihoods and self-reliance in vulnerable areas of the Goascorán River basin. Overview of the Initiative</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Public Space</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>both individuals and editorial offices, highlighting impactful work in media</t>
-        </is>
-      </c>
+          <t>UN Partner Portal</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>30-Mar-2026</t>
+          <t>26-Mar-2026</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1110,12 +1137,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/mdfoundationUA/posts/pfbid0rLVaWWfquxPyoXfywXYPLzeDZzFozK7jB1z4xhrH3kBq6hawZqbhTWWKVjG3VGFcl</t>
+          <t>https://www.unpartnerportal.org/landing/opportunities/</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/community-development/25-to-25-young-and-bold-competition-ukraine/</t>
+          <t>https://www2.fundsforngos.org/community-development/call-for-eois-climate-services-and-community-sats-honduras/</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1123,27 +1150,28 @@
           <t>https://www2.fundsforngos.org/tag/lebanon/</t>
         </is>
       </c>
+      <c r="J15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Applications open for Youth to the Front Fund</t>
+          <t>Call for EOIs: Fresh Produce Distribution to 185 School Centers (Honduras)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Deadline: 06-Apr-2026 The Youth to the Front Fund supports young creatives under 30 whose work drives measurable social impact. Projects span arts, performance, film, design, technology, and community interventions, focusing on equity, justice, and systemic change, with opportunities for mentorship, collaboration, and visibility across global networks. About the Fund The Youth to the Front Fund</t>
+          <t>Deadline: 24-Mar-2026 The World Food Programme (WFP) is inviting expressions of interest to deliver fresh produce to 185 schools in southern Honduras during the 2026 school year. The initiative aims to reactivate the small producer purchasing model, improve school meal nutrition, boost local economies, and strengthen the capacities of smallholder suppliers linked to the National</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>We Are Family Foundation</t>
+          <t>UN Partner Portal</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>06-Apr-2026</t>
+          <t>24-Mar-2026</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1153,12 +1181,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.wearefamilyfoundation.org/apply-2026-frontliner</t>
+          <t>https://www.unpartnerportal.org/landing/opportunities/</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/community-development/applications-open-for-youth-to-the-front-fund/</t>
+          <t>https://www2.fundsforngos.org/community-development/call-for-eois-fresh-produce-distribution-to-185-school-centers-honduras/</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1166,27 +1194,32 @@
           <t>https://www2.fundsforngos.org/tag/lebanon/</t>
         </is>
       </c>
+      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Call for Applications: Three Dot Dash Program</t>
+          <t>Call for EOIs: Rapid Response Research Grants Program</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Deadline: 19-Mar-2026 The Three Dot Dash Program empowers teenagers leading environmental and community-driven sustainability projects to become Global Teen Leaders. Participants join a year-long leadership development journey, including the 2026 Just Peace Summit in London, mentorship, virtual programming, and a global support network. Applicants must be 13–19 years old, actively leading impactful projects, and committed</t>
+          <t>Deadline: 31-Mar-2026 SUMERNET is inviting Expressions of Interest (EOIs) for 12 rapid-response research grants under SUMERNET PLUS (Phase 5), offering up to 480,000 SEK per project for initiatives in the Mekong Region. Projects must be completed within 6–12 months and can apply under Capacity Development Grants, Impact Grants, or Innovation Grants, with a strong focus</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>We Are Family Foundation</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>SUMERNET</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Cambodia, Lao PDR, Thailand, and Vietnam</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>19-Mar-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1196,12 +1229,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.wearefamilyfoundation.org/three-dot-dash-apply</t>
+          <t>https://www.sumernet.org/story/call-for-expressions-of-interest-rapid-response-grants-under-sumernet-plus-programme</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/community-development/call-for-applications-three-dot-dash-program/</t>
+          <t>https://www2.fundsforngos.org/community-development/call-for-eois-rapid-response-research-grants-program/</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1209,31 +1242,28 @@
           <t>https://www2.fundsforngos.org/tag/lebanon/</t>
         </is>
       </c>
+      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Call for EOIs: Climate-Resilient WASH Services in Karamoja (Uganda)</t>
+          <t>Call for Proposals: Citizen Security Research Initiative</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Deadline: 07-Apr-2026 The UNICEF Uganda WASH Grants 2030 support initiatives that improve water, sanitation, hygiene (WASH), and environmental sustainability for children and families. With an indicative budget of $282,177, the programme focuses on climate-resilient infrastructure, safe hygiene practices, and system strengthening. The goal is to achieve clean, safe, and sustainable communities by 2030. What is</t>
+          <t>Deadline: 15-Apr-2026 The CSRI invites researchers to submit proposals for projects generating actionable evidence to strengthen justice systems, law enforcement, and community safety. Funding supports pilot studies, full impact evaluations, infrastructure creation, and foundational research, with grants ranging from $75,000 to $400,000. About the Initiative The CSRI aims to inform policies and programs that enhance</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>UN Partner Portal</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Uganda (selected regions)</t>
-        </is>
-      </c>
+          <t>IPA</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>07-Apr-2026</t>
+          <t>15-Apr-2026</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1243,12 +1273,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.unpartnerportal.org/landing/opportunities/</t>
+          <t>https://poverty-action.org/csri-call-for-proposals</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/community-development/call-for-eois-climate-resilient-wash-services-in-karamoja-uganda/</t>
+          <t>https://www2.fundsforngos.org/community-development/call-for-proposals-citizen-security-research-initiative/</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1256,31 +1286,32 @@
           <t>https://www2.fundsforngos.org/tag/lebanon/</t>
         </is>
       </c>
+      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Call for Operator to Implement Bouaké Urban Nursery (Côte d’Ivoire)</t>
+          <t>CFPs: Implementing Organizations for the Mission-Oriented Economy Programme (Ukraine)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Deadline: 04-May-2026 The Bouaké Urban Nursery Call for Initiatives seeks an operator to implement a cultural and social innovation space in Bouaké under the Cultures Côte d’Ivoire project. Funded by the French Development Agency, the initiative supports participatory urban development, cultural programming, and creative industries. Eligible applicants include NGOs, associations, and consortiums with strong experience</t>
+          <t>Deadline: 25-Mar-2026 The United Nations Development Programme (UNDP) is inviting applications for seed and growth portfolio activities to strengthen the economic sustainability of selected municipalities in Ukraine under the M4EG-III framework. The program supports projects in Zhytomyr, Khmelnytskyi Urban Territorial Community, Bucha, and Slavutych, with grants of up to US$60,000 per portfolio. Overview The UNDP</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AFD</t>
+          <t>UNDP</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>and Timeline</t>
+          <t>Projects must be implemented in one of the following four designated</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>25-Mar-2026</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1290,12 +1321,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.afd.fr/fr/appels-a-projets/pepiniere-urbaine-bouake-cultures-cote-ivoire</t>
+          <t>https://www.undp.org/ukraine/news/call-proposals-implementing-organizations-mission-oriented-economy-programme</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/community-development/call-for-operator-to-implement-bouake-urban-nursery-cote-divoire/</t>
+          <t>https://www2.fundsforngos.org/community-development/cfps-implementing-organizations-for-the-mission-oriented-economy-programme-ukraine/</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1303,27 +1334,32 @@
           <t>https://www2.fundsforngos.org/tag/lebanon/</t>
         </is>
       </c>
+      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Call for Proposals: Citizen Security Research Initiative</t>
+          <t>Community Facilities Enhancement Funding Programme (Ireland)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Deadline: 15-Apr-2026 The CSRI invites researchers to submit proposals for projects generating actionable evidence to strengthen justice systems, law enforcement, and community safety. Funding supports pilot studies, full impact evaluations, infrastructure creation, and foundational research, with grants ranging from $75,000 to $400,000. About the Initiative The CSRI aims to inform policies and programs that enhance</t>
+          <t>Deadline: 27-Mar-2026 The Dublin Rural LEADER is accepting applications for a targeted funding call to support community-led projects that address gaps in rural infrastructure, services, and community amenities across its operational area. Grants range from €50,000 to €150,000, with some higher-merit projects eligible for up to €200,000, and the total budget available is €700,000. Overview</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>IPA</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Dublin Rural Leader</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>a wide range of community-based and mission-driven organisations.</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>15-Apr-2026</t>
+          <t>27-Mar-2026</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1333,12 +1369,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://poverty-action.org/csri-call-for-proposals</t>
+          <t>https://www.fingalleaderpartnership.ie/dublin-rural-leader/blog/community-facilities-enhancement-targeted-call-for-funding</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/community-development/call-for-proposals-citizen-security-research-initiative/</t>
+          <t>https://www2.fundsforngos.org/community-development/community-facilities-enhancement-funding-programme-ireland/</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1346,31 +1382,32 @@
           <t>https://www2.fundsforngos.org/tag/lebanon/</t>
         </is>
       </c>
+      <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CFPs: Women’s and Youth Organizations to Strengthen Communal Peace and Social Cohesion (South Sudan)</t>
+          <t>Open Call: Gender Empowerment Now! Training Programme</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Deadline: 31-Mar-2026 The Peace and Community Cohesion III (PaCC) Programme by the United Nations Development Programme and the Government of South Sudan offers multiple funding opportunities for NGOs and CSOs to promote peacebuilding, social cohesion, and community resilience. The programme targets conflict-affected regions with funding across six thematic slots, addressing violence reduction, women’s leadership, reintegration,</t>
+          <t>Deadline: 20-Mar-2026 The UNITAR Gender Empowerment Now! Training Programme – Cycle 6 supports NGO representatives and independent activists in the Middle East and North Africa to strengthen skills in gender equality, women’s empowerment, and peacebuilding. Selected participants will design and facilitate community workshops, develop training materials, and gain practical tools to advance gender mainstreaming within</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>UNDP</t>
+          <t>UNITAR</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Areas</t>
+          <t>Eligibility requirements include:</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>31-Mar-2026</t>
+          <t>20-Mar-2026</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1380,40 +1417,45 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://procurement-notices.undp.org/view_notice.cfm?notice_id=98794</t>
+          <t>https://unitar.org/about/news-stories/news/call-applications-gender-empowerment-now-women-peace-and-security-cycle-6</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/community-development/cfps-womens-and-youth-organizations-to-strengthen-communal-peace-and-social-cohesion-south-sudan/</t>
+          <t>https://www2.fundsforngos.org/community-development/open-call-gender-empowerment-now-training-programme/</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
           <t>https://www2.fundsforngos.org/tag/lebanon/</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>This grant strengthens the gender equality, women's empowerment, and peacebuilding skills of NGO representatives and independent activists in the Middle East and North Africa to advance gender mainstreaming.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Growth Fund Supporting Social Innovation Scaling (Ireland)</t>
+          <t>Submissions open for the ODI Fellowship Scheme</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Deadline: 20-Apr-2026 The Growth Fund 2026–2029 is a €3.6 million funding initiative in Ireland supporting up to three high-performing organisations to scale proven social innovations. Each selected organisation can receive up to €1.15 million, combining financial support with tailored business assistance. The fund focuses on impact-driven projects in areas such as education, health, equality, and</t>
+          <t>Deadline: 31-Mar-2026 The ODI Fellowship Scheme offers fully funded two-year placements for young professionals in global development, providing opportunities to work within government ministries and agencies worldwide. Fellows gain hands-on experience in economic, statistical, and policy roles while strengthening institutional capacity and advancing their careers in development and public sector organizations. About the Scheme The</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Rethink Ireland</t>
+          <t>ODI Global</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1423,40 +1465,49 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://rethinkireland.ie/current_fund/growthfund2026/</t>
+          <t>https://odi.org/en/fellowship-scheme/</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/community-development/growth-fund-supporting-social-innovation-scaling-ireland/</t>
+          <t>https://www2.fundsforngos.org/community-development/submissions-open-for-the-odi-fellowship-scheme/</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
           <t>https://www2.fundsforngos.org/tag/lebanon/</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>The ODI Fellowship Scheme places young professionals in global development in government roles to strengthen institutional capacity worldwide.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Micro-Projects Grant Opportunity in Nordhorn-Neuenhaus-Lage (Germany)</t>
+          <t>Submit Applications for Direct Action Visionary Grant Program (US)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Deadline: 01-May-2026 The Nordhorn–Neuenhaus–Lage Micro-Project Funding Programme 2026 provides small grants of up to €2,500 to support community-driven initiatives that improve public spaces and local cohesion. With a total funding pool of €30,000, the programme aims to strengthen civic engagement, social interaction, and village development. Eligible applicants include associations, institutions, parishes, and individuals in the</t>
+          <t>Deadline: 30-Apr-2026 The APF Direct Action Visionary Grants support innovative, evidence-based psychological interventions that respond directly to urgent community needs. The program offers up to $60,000 for projects that create immediate, measurable impact, especially for marginalized communities facing prejudice, stigma, violence, or health inequities. About the Grant The APF Direct Action Visionary Grants fund projects</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Samtgemeinde Neuenhaus</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>American Psychological Foundation</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>individuals and organizations</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>01-May-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1466,44 +1517,49 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.neuenhaus.de/:translation/en/samtgemeinde-neuenhaus/start/samtgemeinde/aktuelles/neuigkeiten/2026/aufruf-zur-bewerbung-fuer-kleinstvorhaben/</t>
+          <t>https://ampsychfdn.org/funding/direct-action-visionary-grants/</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/community-development/micro-projects-grant-opportunity-in-nordhorn-neuenhaus-lage-germany/</t>
+          <t>https://www2.fundsforngos.org/community-development/submit-applications-for-direct-action-visionary-grant-program-us/</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>https://www2.fundsforngos.org/tag/lebanon/</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>This grant supports innovative psychological interventions that deliver immediate impact for marginalized communities experiencing prejudice, stigma, violence, or health inequities.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Open Call: Gender Empowerment Now! Training Programme</t>
+          <t>7th Edition of the “La Francophonie avec Elles” Fund</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Deadline: 20-Mar-2026 The UNITAR Gender Empowerment Now! Training Programme – Cycle 6 supports NGO representatives and independent activists in the Middle East and North Africa to strengthen skills in gender equality, women’s empowerment, and peacebuilding. Selected participants will design and facilitate community workshops, develop training materials, and gain practical tools to advance gender mainstreaming within</t>
+          <t>Deadline: 26-Apr-2026 The International Organisation of the Francophonie (OIF) has launched the 7th edition of the “La Francophonie avec Elles” Fund to support socio-economic empowerment of women and girls. The initiative provides grants of up to €100,000 for projects promoting vocational training, entrepreneurship, and sustainable economic opportunities for vulnerable women across OIF member states. Project</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>UNITAR</t>
+          <t>OIF</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Eligibility requirements include:</t>
+          <t>for the Fund?</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>20-Mar-2026</t>
+          <t>26-Apr-2026</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1513,44 +1569,45 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://unitar.org/about/news-stories/news/call-applications-gender-empowerment-now-women-peace-and-security-cycle-6</t>
+          <t>https://www.francophonie.org/index.php/appel-candidatures-7e-edition-fonds-la-francophonie-avec-elles-8391</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/community-development/open-call-gender-empowerment-now-training-programme/</t>
+          <t>https://www2.fundsforngos.org/economic-development/7th-edition-of-the-la-francophonie-avec-elles-fund/</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>https://www2.fundsforngos.org/tag/lebanon/</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>This grant opportunity aims to socio-economically empower vulnerable women and girls through vocational training, entrepreneurship, and sustainable economic opportunities.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>RFPs: Promoting Regenerative Agriculture System through Safe Farming Practices (Nepal)</t>
+          <t>TIAW World of Difference Awards for Women’s Economic Empowerment</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Deadline: 03-Apr-2026 The United Nations Development Programme Nepal, in partnership with Dhangadhi Sub-Metropolitan City, is seeking service providers to operationalize agricultural collection centers and strengthen market linkages. The initiative focuses on green jobs, climate-resilient farming, and sustainable livelihoods under the Green Transition Portfolio. Eligible applicants must have experience in sustainable agriculture, farmer training, and community-based</t>
+          <t>Deadline: 22-May-2026 The International Alliance for Women (TIAW) World of Difference Awards honor individuals and organizations advancing women’s economic empowerment globally. Awards recognize impactful initiatives in entrepreneurship, education, corporate leadership, public sector work, and community projects, with additional lifetime and member-specific recognitions. What Are the TIAW World of Difference Awards? The TIAW World of Difference</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>UNDP</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Location:</t>
-        </is>
-      </c>
+          <t>The International Alliance for Women</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>03-Apr-2026</t>
+          <t>22-May-2026</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1560,40 +1617,49 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://procurement-notices.undp.org/view_negotiation.cfm?nego_id=43727</t>
+          <t>https://tiaw.org/awards/</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/community-development/rfps-promoting-regenerative-agriculture-system-through-safe-farming-practices-nepal/</t>
+          <t>https://www2.fundsforngos.org/economic-development/tiaw-world-of-difference-awards-for-womens-economic-empowerment/</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
           <t>https://www2.fundsforngos.org/tag/lebanon/</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>The TIAW World of Difference Awards recognize individuals and organizations globally for their impactful work in advancing women's economic empowerment.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Submissions open for the ODI Fellowship Scheme</t>
+          <t>Advancing Racial Equity in Education Through Research Grants</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Deadline: 31-Mar-2026 The ODI Fellowship Scheme offers fully funded two-year placements for young professionals in global development, providing opportunities to work within government ministries and agencies worldwide. Fellows gain hands-on experience in economic, statistical, and policy roles while strengthening institutional capacity and advancing their careers in development and public sector organizations. About the Scheme The</t>
+          <t>Deadline: 04-May-2026 The Spencer Foundation Racial Equity Research Grants Program provides funding of up to $75,000 for research addressing racial inequality in education.It supports rigorous, innovative studies across all education levels worldwide to generate actionable insights and advance educational equity. What is the Program About? The Racial Equity Research Grants Program funds academic research projects</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ODI Global</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t>The Spencer Foundation</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>global applicants</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>31-Mar-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1603,44 +1669,49 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://odi.org/en/fellowship-scheme/</t>
+          <t>https://www.spencer.org/grant_types/racial-equity-special-research-grants</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/community-development/submissions-open-for-the-odi-fellowship-scheme/</t>
+          <t>https://www2.fundsforngos.org/education/advancing-racial-equity-in-education-through-research-grants/</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
           <t>https://www2.fundsforngos.org/tag/lebanon/</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>The Spencer Foundation offers grants for research aimed at addressing racial inequality in education to advance educational equity for learners worldwide.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Apply now for Canada Fund for Local Initiatives 2026</t>
+          <t>Applications open for Educational Scholarship</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Deadline: 30-Apr-2026 The Canada Fund for Local Initiatives (CFLI) – ASEAN 2026 by Global Affairs Canada supports small-scale, high-impact projects across ASEAN countries. Grants typically range from CAD 20,000 to CAD 40,000, with a maximum of CAD 100,000 per project. The program prioritizes inclusive governance, peace and security, and inclusive economic growth, with strong emphasis</t>
+          <t>Deadline: 17-Apr-2026 The Slow Food Educational Scholarship supports emerging beverage professionals to attend global industry events focused on sustainability, networking, and skill-building. Selected participants gain full event registration, lodging, travel stipends, and mentorship, while deepening knowledge of sustainable practices and the Slow Food values of good, clean, and fair food and beverage. This initiative targets</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Government of Canada</t>
+          <t>Slow Food</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Measurable outcomes</t>
+          <t>for the Slow Food Educational Scholarship?</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1650,12 +1721,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.international.gc.ca/world-monde/funding-financement/cfli-fcil/asean-anase.aspx?lang=eng</t>
+          <t>https://www.slowfood.com/it/insights/calls-for-proposals/</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/democracy-good-governance/apply-now-for-canada-fund-for-local-initiatives-2026/</t>
+          <t>https://www2.fundsforngos.org/education/applications-open-for-educational-scholarship/</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1663,31 +1734,28 @@
           <t>https://www2.fundsforngos.org/tag/lebanon/</t>
         </is>
       </c>
+      <c r="J27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>7th Edition of the “La Francophonie avec Elles” Fund</t>
+          <t>Apply for Gender and Transportation E-Learning Course</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Deadline: 26-Apr-2026 The International Organisation of the Francophonie (OIF) has launched the 7th edition of the “La Francophonie avec Elles” Fund to support socio-economic empowerment of women and girls. The initiative provides grants of up to €100,000 for projects promoting vocational training, entrepreneurship, and sustainable economic opportunities for vulnerable women across OIF member states. Project</t>
+          <t>Deadline: 31-Dec-2026 This E-learning course on Gender and Transportation explores how gender equality and inclusive mobility are connected within the broader development context. The course helps learners understand how transport systems affect women and girls, why gender-responsive transportation matters, and how more inclusive mobility systems can improve access, safety, participation, and equitable development outcomes. It</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>OIF</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>for the Fund?</t>
-        </is>
-      </c>
+          <t>UN Women</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>26-Apr-2026</t>
+          <t>31-Dec-2026</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1697,12 +1765,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.francophonie.org/index.php/appel-candidatures-7e-edition-fonds-la-francophonie-avec-elles-8391</t>
+          <t>https://portal.trainingcentre.unwomen.org/product/gender-and-transportation/</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/economic-development/7th-edition-of-the-la-francophonie-avec-elles-fund/</t>
+          <t>https://www2.fundsforngos.org/education/apply-for-gender-and-transportation-e-learning-course/</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1710,31 +1778,28 @@
           <t>https://www2.fundsforngos.org/tag/lebanon/</t>
         </is>
       </c>
+      <c r="J28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Call for Proposals:  Innovation Grants 2026 (Philippines)</t>
+          <t>Apply Now: Advancing Crime Statistics Through a Gender Perspective</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Deadline: 05-May-2026 The 2026 Innovation Grants in the Philippines provide PHP 100 million in funding for government-led innovation projects under the Philippine Innovation Act (RA 11293). Managed by the Department of Economy, Planning, and Development (DEPDev), the program supports inclusive growth, MSME integration, and solutions benefiting marginalized communities. Eligible public institutions can apply by submitting</t>
+          <t>Deadline: 31-Dec-2026 This self-paced online course, supported by UN Women, equips professionals with the skills to integrate a gender perspective into crime statistics. Participants learn to collect, analyze, and disseminate crime data considering gender, including SDG indicators, femicide, and technology-facilitated violence against women, to support evidence-based policymaking. Overview of the Course The course emphasizes the</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Department of Planning, Economy and Development</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>for the Innovation Grants?</t>
-        </is>
-      </c>
+          <t>UN Women.</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>05-May-2026</t>
+          <t>31-Dec-2026</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1744,12 +1809,12 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/photo?fbid=1207981411505427&amp;set=pcb.1207981571505411</t>
+          <t>https://portal.trainingcentre.unwomen.org/product/crime-statistics-from-a-gender-perspective/</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/economic-development/call-for-proposals-innovation-grants-2026-philippines/</t>
+          <t>https://www2.fundsforngos.org/education/apply-now-advancing-crime-statistics-through-a-gender-perspective/</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1757,27 +1822,28 @@
           <t>https://www2.fundsforngos.org/tag/lebanon/</t>
         </is>
       </c>
+      <c r="J29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>TIAW World of Difference Awards for Women’s Economic Empowerment</t>
+          <t>AWIU Global Micro-Grants for Women’s Empowerment</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Deadline: 22-May-2026 The International Alliance for Women (TIAW) World of Difference Awards honor individuals and organizations advancing women’s economic empowerment globally. Awards recognize impactful initiatives in entrepreneurship, education, corporate leadership, public sector work, and community projects, with additional lifetime and member-specific recognitions. What Are the TIAW World of Difference Awards? The TIAW World of Difference</t>
+          <t>Deadline: 16-Apr-2026 The AWIU Global Micro-Grants program funds grassroots women-led initiatives in low and middle-income countries, focusing on education, health, and entrepreneurship. Grants of up to USD 3,000 support short-term, measurable projects with scalable community impact, enhancing women’s wellbeing and fostering sustainable development. About the Program The AWIU Global Micro-Grants program supports small-scale, high-impact projects</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>The International Alliance for Women</t>
+          <t>AWIU</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>22-May-2026</t>
+          <t>16-Apr-2026</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1787,12 +1853,12 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://tiaw.org/awards/</t>
+          <t>https://awiu.org/global-micro-grants/</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/economic-development/tiaw-world-of-difference-awards-for-womens-economic-empowerment/</t>
+          <t>https://www2.fundsforngos.org/education/awiu-global-micro-grants-for-womens-empowerment/</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1800,31 +1866,32 @@
           <t>https://www2.fundsforngos.org/tag/lebanon/</t>
         </is>
       </c>
+      <c r="J30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Advancing Racial Equity in Education Through Research Grants</t>
+          <t>Call for Applications: Visionary Grant Program (US)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Deadline: 04-May-2026 The Spencer Foundation Racial Equity Research Grants Program provides funding of up to $75,000 for research addressing racial inequality in education.It supports rigorous, innovative studies across all education levels worldwide to generate actionable insights and advance educational equity. What is the Program About? The Racial Equity Research Grants Program funds academic research projects</t>
+          <t>Deadline: 03-Apr-2026 The American Psychological Foundation (APF) Visionary Grants support innovative research, education, and intervention projects that use psychology to address major social problems. In 2026, the program will award 10 grants of up to $20,000 each, with preference for pilot and demonstration projects that show practical impact and strong potential for future funding. This</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>The Spencer Foundation</t>
+          <t>American Psychological Foundation</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>global applicants</t>
+          <t>graduate students and early-career researchers</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>03-Apr-2026</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1834,12 +1901,12 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.spencer.org/grant_types/racial-equity-special-research-grants</t>
+          <t>https://ampsychfdn.org/funding/visionary-grants/</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/education/advancing-racial-equity-in-education-through-research-grants/</t>
+          <t>https://www2.fundsforngos.org/education/call-for-applications-visionary-grant-program-us/</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1847,31 +1914,28 @@
           <t>https://www2.fundsforngos.org/tag/lebanon/</t>
         </is>
       </c>
+      <c r="J31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Applications open for Educational Scholarship</t>
+          <t>Call for Expression of Interest: Emergency Education Support (Colombia)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Deadline: 17-Apr-2026 The Slow Food Educational Scholarship supports emerging beverage professionals to attend global industry events focused on sustainability, networking, and skill-building. Selected participants gain full event registration, lodging, travel stipends, and mentorship, while deepening knowledge of sustainable practices and the Slow Food values of good, clean, and fair food and beverage. This initiative targets</t>
+          <t>Deadline: 27-Mar-2026 UNICEF is seeking expressions of interest (EOIs) from qualified implementing partners to support emergency education responses for children and adolescents affected by armed conflict, climate-related disasters, and displacement in prioritized areas of Colombia. With an indicative budget of 300,000, the opportunity focuses on education in emergencies, safe learning spaces, out-of-school education, learning recovery,</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Slow Food</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>for the Slow Food Educational Scholarship?</t>
-        </is>
-      </c>
+          <t>UN Partner Portal</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>27-Mar-2026</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1881,12 +1945,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.slowfood.com/it/insights/calls-for-proposals/</t>
+          <t>https://www.unpartnerportal.org/landing/opportunities/</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/education/applications-open-for-educational-scholarship/</t>
+          <t>https://www2.fundsforngos.org/education/call-for-expression-of-interest-emergency-education-support-colombia/</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1894,27 +1958,28 @@
           <t>https://www2.fundsforngos.org/tag/lebanon/</t>
         </is>
       </c>
+      <c r="J32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AWIU Global Micro-Grants for Women’s Empowerment</t>
+          <t>Call for Nominations: UNESCO Prize for Girls’ and Women’s Education</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Deadline: 16-Apr-2026 The AWIU Global Micro-Grants program funds grassroots women-led initiatives in low and middle-income countries, focusing on education, health, and entrepreneurship. Grants of up to USD 3,000 support short-term, measurable projects with scalable community impact, enhancing women’s wellbeing and fostering sustainable development. About the Program The AWIU Global Micro-Grants program supports small-scale, high-impact projects</t>
+          <t>Deadline: 12-May-2026 The UNESCO Prize for Girls’ and Women’s Education recognizes innovative initiatives that improve educational opportunities for girls and women. Funded by the Government of China, the prize awards two laureates annually with $50,000 USD each to support and expand impactful educational programs. Overview The prize aims to highlight exceptional efforts that: Advance education</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AWIU</t>
+          <t>UNESCO</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>16-Apr-2026</t>
+          <t>12-May-2026</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1924,12 +1989,12 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://awiu.org/global-micro-grants/</t>
+          <t>https://www.unesco.org/en/articles/call-nominations-2026-unesco-prize-girls-and-womens-education-now-open</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/education/awiu-global-micro-grants-for-womens-empowerment/</t>
+          <t>https://www2.fundsforngos.org/education/call-for-nominations-unesco-prize-for-girls-and-womens-education/</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1937,27 +2002,32 @@
           <t>https://www2.fundsforngos.org/tag/lebanon/</t>
         </is>
       </c>
+      <c r="J33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Call for Nominations: UNESCO Prize for Girls’ and Women’s Education</t>
+          <t>Call for Submissions: Z Zurich Foundation Scholarship (Africa)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Deadline: 12-May-2026 The UNESCO Prize for Girls’ and Women’s Education recognizes innovative initiatives that improve educational opportunities for girls and women. Funded by the Government of China, the prize awards two laureates annually with $50,000 USD each to support and expand impactful educational programs. Overview The prize aims to highlight exceptional efforts that: Advance education</t>
+          <t>Deadline: 04-May-2026 The Z Zurich Foundation Scholarship 2026 is now open to support 25 young African changemakers working to help youth move from learning to earning through education, employment, and entrepreneurship. Selected scholars will receive fully funded participation in the One Young World Summit 2026 in Cape Town, South Africa, along with leadership development, networking,</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>UNESCO</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
+          <t>Z Zurich Foundation</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>support</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>12-May-2026</t>
+          <t>04-May-2026</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1967,12 +2037,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.unesco.org/en/articles/call-nominations-2026-unesco-prize-girls-and-womens-education-now-open</t>
+          <t>https://www.oneyoungworld.com/scholarship/z-zurich-foundation-scholarship-2026</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/education/call-for-nominations-unesco-prize-for-girls-and-womens-education/</t>
+          <t>https://www2.fundsforngos.org/education/call-for-submissions-z-zurich-foundation-scholarship-africa/</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -1980,27 +2050,28 @@
           <t>https://www2.fundsforngos.org/tag/lebanon/</t>
         </is>
       </c>
+      <c r="J34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Entries Open: Intercultural Achievement Award 2026</t>
+          <t>E-Learning Program: Gender Analysis for Digital Inclusion</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Deadline: 31-Mar-2026 The Intercultural Achievement Award 2026, offered by the Austrian Federal Ministry for European and International Affairs, recognizes impactful projects that promote intercultural and interreligious dialogue. Winning initiatives can receive EUR 6,000 per category and must demonstrate innovation, sustainability, and measurable societal impact. Eligible applicants include non-profit organizations, associations, foundations, and private-sector organizations working</t>
+          <t>Deadline: 31-Dec-2026 UN Women offers a free, self-paced e-learning course to empower individuals to advance gender equality in the digital sector. The course covers gender analysis, digital inclusion, and practical strategies to implement gender-sensitive approaches in professional work, taking approximately two hours to complete online. About the Course This e-learning course, supported by UN Women,</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Federal Ministry for European and International Affairs</t>
+          <t>UN Women.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>31-Mar-2026</t>
+          <t>31-Dec-2026</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2010,12 +2081,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.bmeia.gv.at/en/european-foreign-policy/international-cultural-policy/iaa/call-for-applications</t>
+          <t>https://portal.trainingcentre.unwomen.org/product/gender-analysis-for-digital-inclusion/</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/education/entries-open-intercultural-achievement-award-2026/</t>
+          <t>https://www2.fundsforngos.org/education/e-learning-program-gender-analysis-for-digital-inclusion/</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2023,31 +2094,28 @@
           <t>https://www2.fundsforngos.org/tag/lebanon/</t>
         </is>
       </c>
+      <c r="J35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Fairways Foundation Grant to support Conservation-Based Projects</t>
+          <t>Entries Open: Intercultural Achievement Award 2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Deadline: 30-Apr-2026 The FairWays Foundation funds conservation-focused projects that promote sustainable environmental practices within golf courses and professional turf or ornamental management. The program supports initiatives related to water conservation, habitat stewardship, and water education that create measurable, long-term environmental impact. Eligible organizations must demonstrate clear strategies, measurable outcomes, and alignment with the foundation’s conservation</t>
+          <t>Deadline: 31-Mar-2026 The Intercultural Achievement Award 2026, offered by the Austrian Federal Ministry for European and International Affairs, recognizes impactful projects that promote intercultural and interreligious dialogue. Winning initiatives can receive EUR 6,000 per category and must demonstrate innovation, sustainability, and measurable societal impact. Eligible applicants include non-profit organizations, associations, foundations, and private-sector organizations working</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>The FairWays Foundation</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>for the grant?</t>
-        </is>
-      </c>
+          <t>Federal Ministry for European and International Affairs</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2057,12 +2125,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://thefairwaysfoundation.com/apply/</t>
+          <t>https://www.bmeia.gv.at/en/european-foreign-policy/international-cultural-policy/iaa/call-for-applications</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/education/fairways-foundation-grant-to-support-conservation-based-projects/</t>
+          <t>https://www2.fundsforngos.org/education/entries-open-intercultural-achievement-award-2026/</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2070,27 +2138,32 @@
           <t>https://www2.fundsforngos.org/tag/lebanon/</t>
         </is>
       </c>
+      <c r="J36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>McKinsey.org Forward Learning Program</t>
+          <t>Fairways Foundation Grant to support Conservation-Based Projects</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Deadline: 20-Apr-2026 The McKinsey.org Forward Learning Program equips career starters and job changers in the Middle East and Pakistan with practical skills for the future of work. Participants gain training in problem-solving, communication, digital and AI-enabled solutions, adaptability, and workplace well-being through a 10-week structured learning journey. Overview The Forward Learning Program helps participants: Transform</t>
+          <t>Deadline: 30-Apr-2026 The FairWays Foundation funds conservation-focused projects that promote sustainable environmental practices within golf courses and professional turf or ornamental management. The program supports initiatives related to water conservation, habitat stewardship, and water education that create measurable, long-term environmental impact. Eligible organizations must demonstrate clear strategies, measurable outcomes, and alignment with the foundation’s conservation</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>McKinsey.org</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
+          <t>The FairWays Foundation</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>for the grant?</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2100,12 +2173,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.mckinsey.org/our-programs/forward/locations/middle-east-and-pakistan</t>
+          <t>https://thefairwaysfoundation.com/apply/</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/education/mckinsey-org-forward-learning-program/</t>
+          <t>https://www2.fundsforngos.org/education/fairways-foundation-grant-to-support-conservation-based-projects/</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2113,26 +2186,27 @@
           <t>https://www2.fundsforngos.org/tag/lebanon/</t>
         </is>
       </c>
+      <c r="J37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Call for Applications: MCS Foundation Main Grant (UK)</t>
+          <t>John S. Latsis Public Benefit Foundation Grant Program (Greece)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Deadline: 31-Mar-2026 The MCS Foundation Main Grant Call 2026 offers up to £50,000 per project to support innovative solutions that reduce carbon emissions and transform home energy systems across the UK. With a total fund of £400,000, the program prioritizes projects focused on heat pump efficiency, data use, low-carbon commissioning, and retrofit demand. Open to</t>
+          <t>Deadline: 31-Mar-2026 The John S. Latsis Public Benefit Foundation has opened its 2026 application period for unsolicited grant requests from Civil Society Organisations (CSOs) for non-profit projects in Greece. Selected projects will begin implementation and receive funding in 2027, with applications accepted only through the Foundation’s online form until 31 March 2026 at 18:00 (Greece</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MCS Foundation</t>
+          <t>John S. Latsis Public Benefit Foundation</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>charities, CICs, and public bodies, the grants aim to accelerate the transition to affordable, energy-efficient, and carbon-free homes.</t>
+          <t>The Foundation funds projects</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2147,12 +2221,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://mcsfoundation.org.uk/funding/main-grants/</t>
+          <t>https://www.latsis-foundation.org/eng/public-calls/public-call-for-unsolicited-grant-requests-2026</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/environment/call-for-applications-mcs-foundation-main-grant-uk/</t>
+          <t>https://www2.fundsforngos.org/education/john-s-latsis-public-benefit-foundation-grant-program-greece/</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2160,31 +2234,28 @@
           <t>https://www2.fundsforngos.org/tag/lebanon/</t>
         </is>
       </c>
+      <c r="J38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Submissions open for Climate Curve Prize: Methane</t>
+          <t>McKinsey.org Forward Learning Program</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Deadline: 17-Apr-2026 The Climate Curve Prize: Methane invites innovators to develop solutions that reduce methane emissions from food and waste systems. The global prize provides $25,000 to eight laureates, offering funding, mentorship, and access to climate networks to scale high-impact solutions. About the Prize The Climate Curve Prize: Methane is the first global initiative dedicated</t>
+          <t>Deadline: 20-Apr-2026 The McKinsey.org Forward Learning Program equips career starters and job changers in the Middle East and Pakistan with practical skills for the future of work. Participants gain training in problem-solving, communication, digital and AI-enabled solutions, adaptability, and workplace well-being through a 10-week structured learning journey. Overview The Forward Learning Program helps participants: Transform</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Climate Curve</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>innovators and change-makers</t>
-        </is>
-      </c>
+          <t>McKinsey.org</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2194,12 +2265,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.climatecurve.org/methane</t>
+          <t>https://www.mckinsey.org/our-programs/forward/locations/middle-east-and-pakistan</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/environment/submissions-open-for-climate-curve-prize-methane/</t>
+          <t>https://www2.fundsforngos.org/education/mckinsey-org-forward-learning-program/</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2207,31 +2278,28 @@
           <t>https://www2.fundsforngos.org/tag/lebanon/</t>
         </is>
       </c>
+      <c r="J39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>The Wolfgang Kiessling International Prize for Species Conservation</t>
+          <t>Open Call: Strengthening Plastic Waste Collection Systems in Djibouti</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Deadline: 01-Jun-2026 The Wolfgang Kiessling International Prize for Species Conservation recognizes exceptional conservation scientists whose work combats the Sixth Mass Extinction and preserves global biodiversity. The 2026 prize awards US$80,000 in unrestricted funding to support continued research and conservation projects, with winners presenting their work at an award ceremony in Washington, DC. Applicants must be</t>
+          <t>Deadline: 09-Apr-2026 UNICEF Djibouti is seeking associations or NGOs to conduct an analytical study and develop an operational plastic waste collection chain to support a recycling plant. The initiative focuses on waste management, environmental protection, social inclusion, and sector scaling, aiming to collect at least 5 tons of plastic waste per day through sustainable and</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Global Humane Society</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>for the Wolfgang Kiessling Prize?</t>
-        </is>
-      </c>
+          <t>UN Partner Portal</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>01-Jun-2026</t>
+          <t>09-Apr-2026</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2241,12 +2309,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.globalhumane.org/what-we-do/champion-conservation/</t>
+          <t>https://www.unpartnerportal.org/landing/opportunities/</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/environment/the-wolfgang-kiessling-international-prize-for-species-conservation/</t>
+          <t>https://www2.fundsforngos.org/environment/open-call-strengthening-plastic-waste-collection-systems-in-djibouti/</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2254,31 +2322,32 @@
           <t>https://www2.fundsforngos.org/tag/lebanon/</t>
         </is>
       </c>
+      <c r="J40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Call for Submissions: Talent Latent Photography Programme 2026</t>
+          <t>Request for Proposals: Knowledge Product Development</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Deadline: 12-Apr-2026 The SCAN international photography festival, organised by Tarragona City Council, invites submissions for the Talent Latent program. Emerging photographers worldwide are encouraged to explore the theme Metamorphosis, creating projects that reflect personal, societal, and environmental transformations. Selected works will be exhibited at Tinglado 2, Port of Tarragona, from 16 October to 29 November</t>
+          <t>Deadline: 17-Apr-2026 The Critical Ecosystem Partnership Fund (CEPF) is seeking proposals to develop a participatory, evidence-based knowledge product to improve ecological restoration in the Comoros. The consultancy supports evaluation, identification of good practices, stakeholder engagement, and the design of an actionable output, with funding up to USD 40,000 between 15 April and 31 October 2026.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>SCAN</t>
+          <t>CEPF</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>all nationalities</t>
+          <t>Maximum of USD 40,000, covering research, stakeholder engagement, product development, and dissemination activities</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>12-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2288,12 +2357,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://scan.cat/en/call-for-submissions-talent-latent/</t>
+          <t>https://www.cepf.net/grants/open-calls-for-proposals/2026-knowledge-product-development-comoros-ecological-restoration</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/events/call-for-submissions-talent-latent-photography-programme-2026/</t>
+          <t>https://www2.fundsforngos.org/environment/request-for-proposals-knowledge-product-development/</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2301,31 +2370,32 @@
           <t>https://www2.fundsforngos.org/tag/lebanon/</t>
         </is>
       </c>
+      <c r="J41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Submissions Open: International Videominute Contest 2026</t>
+          <t>Call for Submissions: Talent Latent Photography Programme 2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Deadline: 30-Apr-2026 The Universidad de Zaragoza, in collaboration with Cinemaremagnum Servicios Audiovisuales, invites submissions for the XXV International Videominute Contest. The competition encourages creative short audiovisual works under one minute and awards prizes for the best international, Spanish, and Aragonese videominutes, as well as a special equality mention. About the Contest The Area of Culture</t>
+          <t>Deadline: 12-Apr-2026 The SCAN international photography festival, organised by Tarragona City Council, invites submissions for the Talent Latent program. Emerging photographers worldwide are encouraged to explore the theme Metamorphosis, creating projects that reflect personal, societal, and environmental transformations. Selected works will be exhibited at Tinglado 2, Port of Tarragona, from 16 October to 29 November</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Department of Culture and Heritage</t>
+          <t>SCAN</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>all individuals</t>
+          <t>all nationalities</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>12-Apr-2026</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2335,12 +2405,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://cultura.unizar.es/regulations-videominute-international-contest</t>
+          <t>https://scan.cat/en/call-for-submissions-talent-latent/</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/events/submissions-open-international-videominute-contest-2026/</t>
+          <t>https://www2.fundsforngos.org/events/call-for-submissions-talent-latent-photography-programme-2026/</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2348,31 +2418,32 @@
           <t>https://www2.fundsforngos.org/tag/lebanon/</t>
         </is>
       </c>
+      <c r="J42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Counter Histories Grant: Reframing Puerto Rico Through Photography</t>
+          <t>Submissions Open: International Videominute Contest 2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Deadline: 01-Apr-2026 The Counter Histories Fellowship supports photographers and artists engaging with Puerto Rico and its diaspora to reframe history and address urgent contemporary issues. Fellows receive a $10,000 project development grant, participate in virtual programming, and attend an in-person symposium, fostering professional development, collaboration, and the creation of visual archives. About the Fellowship Counter</t>
+          <t>Deadline: 30-Apr-2026 The Universidad de Zaragoza, in collaboration with Cinemaremagnum Servicios Audiovisuales, invites submissions for the XXV International Videominute Contest. The competition encourages creative short audiovisual works under one minute and awards prizes for the best international, Spanish, and Aragonese videominutes, as well as a special equality mention. About the Contest The Area of Culture</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Magnum Foundation</t>
+          <t>Department of Culture and Heritage</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>All skill levels welcome:</t>
+          <t>all individuals</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>01-Apr-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2382,12 +2453,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.magnumfoundation.org/news/counter-histories-puerto-rico-2026-open-call</t>
+          <t>https://cultura.unizar.es/regulations-videominute-international-contest</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/grant/counter-histories-grant-reframing-puerto-rico-through-photography/</t>
+          <t>https://www2.fundsforngos.org/events/submissions-open-international-videominute-contest-2026/</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2395,31 +2466,32 @@
           <t>https://www2.fundsforngos.org/tag/lebanon/</t>
         </is>
       </c>
+      <c r="J43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Call for Proposals: Direct Action Crisis Funding (US)</t>
+          <t>Counter Histories Grant: Reframing Puerto Rico Through Photography</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Deadline: 23-Mar-2026 The American Psychological Foundation (APF) Direct Action Crisis Funding provides urgent support to doctoral students and early-career psychologists who have lost research funding. Grants cover essential project activities like completing data collection, analyzing existing data, writing outputs, closing projects responsibly with community partners, or preparing new proposals. The program prioritizes research that serves</t>
+          <t>Deadline: 01-Apr-2026 The Counter Histories Fellowship supports photographers and artists engaging with Puerto Rico and its diaspora to reframe history and address urgent contemporary issues. Fellows receive a $10,000 project development grant, participate in virtual programming, and attend an in-person symposium, fostering professional development, collaboration, and the creation of visual archives. About the Fellowship Counter</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>American Psychological Foundation</t>
+          <t>Magnum Foundation</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Why It Matters</t>
+          <t>All skill levels welcome:</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>23-Mar-2026</t>
+          <t>01-Apr-2026</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2429,12 +2501,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://ampsychfdn.org/funding/dacf/</t>
+          <t>https://www.magnumfoundation.org/news/counter-histories-puerto-rico-2026-open-call</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/health/call-for-proposals-direct-action-crisis-funding-us/</t>
+          <t>https://www2.fundsforngos.org/grant/counter-histories-grant-reframing-puerto-rico-through-photography/</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2442,27 +2514,28 @@
           <t>https://www2.fundsforngos.org/tag/lebanon/</t>
         </is>
       </c>
+      <c r="J44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Open Call: Design by Biomedical Undergraduate Teams (DEBUT) Challenge – US</t>
+          <t>CFPs: Novel Interventions Targeting Placental and Gut Inflammation to Improve Fetal Growth</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Deadline: 05-Jun-2026 The DEBUT Challenge invites undergraduate student teams to develop innovative biomedical solutions addressing unmet health and clinical needs. Sponsored by the National Institute of Biomedical Imaging and Bioengineering (NIBIB) and VentureWell, this competition emphasizes design innovation, teamwork, technical communication, and market potential. Winning teams receive monetary awards, commercialization training, and recognition at the</t>
+          <t>Deadline: 28-Apr-2026 The Gates Foundation invites proposals for innovative interventions targeting placental and gut inflammation and oxidative stress to improve fetal growth outcomes. Projects can span mechanism discovery, candidate validation, and early clinical proof-of-concept, with funding up to $1,000,000 depending on the track. The challenge prioritizes scalable, mechanistic interventions in high-burden regions like sub-Saharan Africa</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>VentureWell</t>
+          <t>Gates Foundation</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>05-Jun-2026</t>
+          <t>28-Apr-2026</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2472,12 +2545,12 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://venturewell.org/debut/</t>
+          <t>https://gcgh.grandchallenges.org/challenge/novel-interventions-targeting-placental-and-gut-inflammation-improve-fetal-growth</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/health/open-call-design-by-biomedical-undergraduate-teams-debut-challenge-us/</t>
+          <t>https://www2.fundsforngos.org/health/cfps-novel-interventions-targeting-placental-and-gut-inflammation-to-improve-fetal-growth/</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2485,6 +2558,7 @@
           <t>https://www2.fundsforngos.org/tag/lebanon/</t>
         </is>
       </c>
+      <c r="J45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2532,6 +2606,7 @@
           <t>https://www2.fundsforngos.org/tag/lebanon/</t>
         </is>
       </c>
+      <c r="J46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2579,6 +2654,7 @@
           <t>https://www2.fundsforngos.org/tag/lebanon/</t>
         </is>
       </c>
+      <c r="J47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2626,6 +2702,7 @@
           <t>https://www2.fundsforngos.org/tag/lebanon/</t>
         </is>
       </c>
+      <c r="J48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2673,6 +2750,7 @@
           <t>https://www2.fundsforngos.org/tag/lebanon/</t>
         </is>
       </c>
+      <c r="J49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2716,6 +2794,7 @@
           <t>https://www2.fundsforngos.org/tag/lebanon/</t>
         </is>
       </c>
+      <c r="J50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2759,31 +2838,32 @@
           <t>https://www2.fundsforngos.org/tag/lebanon/</t>
         </is>
       </c>
+      <c r="J51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ICT Innovation Programme for Youth Entrepreneurs 2026 (Zambia)</t>
+          <t>Open Call for Bellagio Center Residency Program</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Deadline: 20-Apr-2026 The ZICTA ICT Innovation Programme 2026 supports Zambian youth aged 18–35 in developing and scaling ICT-driven solutions. It offers training, mentorship, and commercialization support to transform innovative ideas into viable businesses. The programme focuses on scalable tech solutions addressing socio-economic challenges. What is the ZICTA ICT Innovation Programme 2026? The ZICTA ICT Innovation</t>
+          <t>Deadline: 20-Mar-2026 The Rockefeller Foundation Bellagio Center Residency Program is accepting applications from leaders, scholars, artists, and practitioners worldwide to advance high-impact projects during a 26-day residency in Lake Como, Italy. Selected residents receive room, board, a private studio, travel support, and access to a global network, with projects expected to align with key themes</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ZICTA</t>
+          <t>The Rockefeller Foundation</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Validate that your idea is ICT-based</t>
+          <t>leaders from around the world</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>20-Apr-2026</t>
+          <t>20-Mar-2026</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2793,12 +2873,12 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.zicta.zm/ict-innovation/about</t>
+          <t>https://www.rockefellerfoundation.org/fellowships-convenings/bellagio-center/residency-program/</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/information-technology/ict-innovation-programme-for-youth-entrepreneurs-2026-zambia/</t>
+          <t>https://www2.fundsforngos.org/innovation/open-call-for-bellagio-center-residency-program/</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2806,31 +2886,28 @@
           <t>https://www2.fundsforngos.org/tag/lebanon/</t>
         </is>
       </c>
+      <c r="J52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Open Call for Bellagio Center Residency Program</t>
+          <t>YIELD Hub 2026: Advancing Youth Leadership in Health and Rights</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Deadline: 20-Mar-2026 The Rockefeller Foundation Bellagio Center Residency Program is accepting applications from leaders, scholars, artists, and practitioners worldwide to advance high-impact projects during a 26-day residency in Lake Como, Italy. Selected residents receive room, board, a private studio, travel support, and access to a global network, with projects expected to align with key themes</t>
+          <t>Deadline: 03-Apr-2026 The YIELD Hub 2026 Action Learning Cycles bring together youth-led organizations, funders, researchers, INGOs, and partners to strengthen youth leadership and advance sexual and reproductive health and rights (SRHR). Participants collaborate on defending SRHR progress, sustainable financing, climate-responsive approaches, and meaningful youth partnership, applying lessons to their institutions and sharing insights with the</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>The Rockefeller Foundation</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>leaders from around the world</t>
-        </is>
-      </c>
+          <t>YIELD Hub</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>20-Mar-2026</t>
+          <t>03-Apr-2026</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2840,12 +2917,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.rockefellerfoundation.org/fellowships-convenings/bellagio-center/residency-program/</t>
+          <t>https://yieldhub.global/alc2026/</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/innovation/open-call-for-bellagio-center-residency-program/</t>
+          <t>https://www2.fundsforngos.org/leadership/yield-hub-2026-advancing-youth-leadership-in-health-and-rights/</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2853,27 +2930,32 @@
           <t>https://www2.fundsforngos.org/tag/lebanon/</t>
         </is>
       </c>
+      <c r="J53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>YIELD Hub 2026: Advancing Youth Leadership in Health and Rights</t>
+          <t>Entries open for the International Pride Awards</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Deadline: 03-Apr-2026 The YIELD Hub 2026 Action Learning Cycles bring together youth-led organizations, funders, researchers, INGOs, and partners to strengthen youth leadership and advance sexual and reproductive health and rights (SRHR). Participants collaborate on defending SRHR progress, sustainable financing, climate-responsive approaches, and meaningful youth partnership, applying lessons to their institutions and sharing insights with the</t>
+          <t>Deadline: 17-Apr-2026 The International Pride Awards are global recognition awards celebrating individuals and organizations advancing LGBTIQ+ equality, inclusion, and human rights. These awards highlight advocacy, policy influence, community support initiatives, and social change efforts. Core Purpose of the Awards 1. Recognize Impactful Contributions Honor individuals and groups creating real change in LGBTIQ+ communities. 2. Promote</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>YIELD Hub</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
+          <t>International Pride Awards</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>both individuals and organizations.</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>03-Apr-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2883,12 +2965,12 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://yieldhub.global/alc2026/</t>
+          <t>https://internationalprideawards.org/en/about/</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/leadership/yield-hub-2026-advancing-youth-leadership-in-health-and-rights/</t>
+          <t>https://www2.fundsforngos.org/lgbtq/entries-open-for-the-international-pride-awards/</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2896,31 +2978,28 @@
           <t>https://www2.fundsforngos.org/tag/lebanon/</t>
         </is>
       </c>
+      <c r="J54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Entries open for the International Pride Awards</t>
+          <t>Celebrate World Water Day with Key Funding Opportunities</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Deadline: 17-Apr-2026 The International Pride Awards are global recognition awards celebrating individuals and organizations advancing LGBTIQ+ equality, inclusion, and human rights. These awards highlight advocacy, policy influence, community support initiatives, and social change efforts. Core Purpose of the Awards 1. Recognize Impactful Contributions Honor individuals and groups creating real change in LGBTIQ+ communities. 2. Promote</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>International Pride Awards</t>
-        </is>
-      </c>
+          <t>[March 2026] World Water Day highlights the significance of freshwater and advocates for the sustainable management of water resources worldwide. It provides a timely opportunity for organizations to scale innovative and community-driven solutions. That is why we have curated a listing of top NGO grants and funding opportunities to support impactful initiatives in the water</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>both individuals and organizations.</t>
+          <t>nominations from eligible organizations worldwide, the Prize recognizes measurable, large-scale impact across the entire food and</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>17-Apr-2026</t>
+          <t>20-May-2026</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2928,14 +3007,10 @@
           <t>view grant link</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>https://internationalprideawards.org/en/about/</t>
-        </is>
-      </c>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/lgbtq/entries-open-for-the-international-pride-awards/</t>
+          <t>https://www2.fundsforngos.org/listing/celebrate-world-water-day-with-key-funding-opportunities/</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2943,31 +3018,28 @@
           <t>https://www2.fundsforngos.org/tag/lebanon/</t>
         </is>
       </c>
+      <c r="J55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Nominations open for 2026 Champions of the Earth Award</t>
+          <t>Funding Opportunities to Combat Racial Discrimination and Promote Justice</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Deadline: 15-Apr-2026 The United Nations Development Programme (UNDP) is accepting nominations for the 2026 Champions of the Earth Award, the UN’s highest environmental honor. The award recognizes leaders and organizations implementing impactful solutions to protect and restore the world’s oceans, focusing on pollution prevention, ecosystem restoration, sustainable blue economies, and science-driven cooperation. Overview of the</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>UNEP</t>
-        </is>
-      </c>
+          <t>[March 2026] On the International Day for the Elimination of Racial Discrimination, we have curated a powerful list of grant opportunities supporting organizations working to promote equality, protect human rights, and challenge systemic injustice. These funding opportunities are designed to empower initiatives that foster inclusion, amplify marginalized voices, and build more just and equitable societies</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>individuals, governments, and organizations</t>
+          <t>applicants of any nationality, the program supports university-linked research aligned with the legacy of Pablo Casals and contemporary social</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>15-Apr-2026</t>
+          <t>06-Apr-2026</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2975,14 +3047,10 @@
           <t>view grant link</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>https://www.unep.org/news-and-stories/press-release/ocean-health-focus-nominations-open-uneps-2026-champions-earth-award</t>
-        </is>
-      </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/livelihood/nominations-open-for-2026-champions-of-the-earth-award/</t>
+          <t>https://www2.fundsforngos.org/listing/funding-opportunities-to-combat-racial-discrimination-and-promote-justice/</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -2990,6 +3058,7 @@
           <t>https://www2.fundsforngos.org/tag/lebanon/</t>
         </is>
       </c>
+      <c r="J56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3037,27 +3106,32 @@
           <t>https://www2.fundsforngos.org/tag/lebanon/</t>
         </is>
       </c>
+      <c r="J57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Eighth Global Environment Facility Assembly Fellowship Program</t>
+          <t>CFAs: Press Exchange and Collaborative Investigations on Energy and Environment (France and Moldova)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Deadline: 31-Mar-2026 The Earth Journalism Network (EJN) is offering fellowships for five journalists from low- and middle-income countries to cover the Eighth Global Environment Facility (GEF) Assembly in Samarkand, Uzbekistan. Fellows will gain access to high-level discussions on climate finance, adaptation strategies, and environmental partnerships, receive mentorship from senior journalists, and get financial support to</t>
+          <t>Deadline: 24-Mar-2026 The CFI has opened applications to select 10 Moldova-based journalists for a France–Moldova press exchange and collaborative investigation programme focused on energy, environment, and climate. The initiative offers fully funded participation in an exchange in France, followed by cross-border investigative collaboration with French journalists. Overview The CFI France–Moldova press exchange programme supports journalists</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Earth Journalism Network</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr"/>
+          <t>CFI</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>experienced journalists based in Moldova.</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>31-Mar-2026</t>
+          <t>24-Mar-2026</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3067,12 +3141,12 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://earthjournalism.net/opportunities/fellowships-to-cover-the-eighth-global-environment-facility-gef-assembly-in-samarkand</t>
+          <t>https://ac.cfi.fr/en/ads/press-exchange-and-collaborative-investigations-on-energy-and-environment-france-moldova/</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/media/eighth-global-environment-facility-assembly-fellowship-program/</t>
+          <t>https://www2.fundsforngos.org/media/cfas-press-exchange-and-collaborative-investigations-on-energy-and-environment-france-and-moldova/</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3080,31 +3154,28 @@
           <t>https://www2.fundsforngos.org/tag/lebanon/</t>
         </is>
       </c>
+      <c r="J58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>The Houssian Foundation Daylight Fund (Canada)</t>
+          <t>Eighth Global Environment Facility Assembly Fellowship Program</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Deadline: 14-Apr-2026 The Daylight Fund 2026 provides operating grants of $10,000 to $25,000 to organizations in Canada working to improve safety for women and gender-diverse people. The fund prioritizes initiatives addressing gender-based violence, discrimination, and access to safe housing and support services, especially in underserved and rural communities. Grants will be awarded in summer 2026.</t>
+          <t>Deadline: 31-Mar-2026 The Earth Journalism Network (EJN) is offering fellowships for five journalists from low- and middle-income countries to cover the Eighth Global Environment Facility (GEF) Assembly in Samarkand, Uzbekistan. Fellows will gain access to high-level discussions on climate finance, adaptation strategies, and environmental partnerships, receive mentorship from senior journalists, and get financial support to</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>The Houssian Foundation</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
+          <t>Earth Journalism Network</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>14-Apr-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3114,12 +3185,12 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://houssianfoundation.org/grants/the-daylight-fund/</t>
+          <t>https://earthjournalism.net/opportunities/fellowships-to-cover-the-eighth-global-environment-facility-gef-assembly-in-samarkand</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/narcotics-drugs-crime/the-houssian-foundation-daylight-fund-canada/</t>
+          <t>https://www2.fundsforngos.org/media/eighth-global-environment-facility-assembly-fellowship-program/</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3127,31 +3198,32 @@
           <t>https://www2.fundsforngos.org/tag/lebanon/</t>
         </is>
       </c>
+      <c r="J59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Call for Applications: Connection Grant Program (Canada)</t>
+          <t>Entries Open: Elizabeth Neuffer Fellowship 2027</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Deadline: 01-May-2026 The Connection Grant Program supports short-term initiatives that foster knowledge exchange and engagement in the social sciences and humanities. Grants fund events, outreach activities, and international collaborations designed to promote interdisciplinary dialogue, intersectoral partnerships, and public engagement. Funding ranges from $10,000 to $50,000, and eligible applicants are affiliated with Canadian postsecondary institutions or</t>
+          <t>Deadline: 19-Apr-2026 The Elizabeth Neuffer Fellowship Program offers a fully funded opportunity for women, nonbinary, and gender non-conforming journalists to strengthen their reporting in human rights and social justice. The fellowship combines academic study and research at MIT’s Center for International Studies with professional newsroom experience through internships at The Boston Globe and The New</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Government of Canada</t>
+          <t>IWMF</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>for a Connection Grant?</t>
+          <t>journalists from</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>01-May-2026</t>
+          <t>19-Apr-2026</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -3161,12 +3233,12 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://sshrc-crsh.canada.ca/en/funding/opportunities/connection-grants/2026/competition.aspx</t>
+          <t>https://www.iwmf.org/programs/neuffer/</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/research/call-for-applications-connection-grant-program-canada/</t>
+          <t>https://www2.fundsforngos.org/media/entries-open-elizabeth-neuffer-fellowship-2027/</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3174,27 +3246,32 @@
           <t>https://www2.fundsforngos.org/tag/lebanon/</t>
         </is>
       </c>
+      <c r="J60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Call for Applications: TWAS-CSIR Postgraduate Fellowship Programme</t>
+          <t>Applications open for Falling Walls Lab Competition Yerevan (Armenia)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Deadline: 06-May-2026 The TWAS-CSIR Postgraduate Fellowship supports foreign scholars from developing countries to pursue PhD research in emerging science and technology areas in India. The program offers Sandwich and Full-Time Fellowships, providing up to four years of funding at CSIR research laboratories and institutes to strengthen scientific capacity and doctoral research opportunities. Overview The fellowship</t>
+          <t>Deadline: 30-Apr-2026 Falling Walls Lab Yerevan is a 3-minute pitch competition for students and early-career professionals to present innovative ideas that can create impact in science and society. Open to applicants aged 18+ from all disciplines, it offers a valuable platform for visibility, networking, and science communication. What is Falling Walls Lab Yerevan? Falling Walls</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>TWAS</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr"/>
+          <t>Falling Walls Foundation</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>applicants aged 18+ from all disciplines, it offers a valuable platform for visibility, networking, and science communication.</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>06-May-2026</t>
+          <t>30-Apr-2026</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3204,12 +3281,12 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://twas.org/opportunity/twas-csir-postgraduate-fellowship-programme</t>
+          <t>https://falling-walls.com/falling-walls-lab-yerevan-armenia-daad</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/research/call-for-applications-twas-csir-postgraduate-fellowship-programme/</t>
+          <t>https://www2.fundsforngos.org/research/applications-open-for-falling-walls-lab-competition-yerevan-armenia/</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3217,31 +3294,28 @@
           <t>https://www2.fundsforngos.org/tag/lebanon/</t>
         </is>
       </c>
+      <c r="J61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Call for Entries: Science and SciLifeLab Prize for Young Scientists</t>
+          <t>Apply now for Walter Katkovsky Research Grant Program (United States)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Deadline: 15-Jul-2026 The SciLifeLab and Science Prize for Young Scientists honors exceptional doctoral research in life sciences, offering winners financial awards, global recognition, and publication opportunities. Each year, four category winners are selected, including a grand prize of USD 30,000, with category winners receiving USD 10,000 each. Winners also gain the chance to present their</t>
+          <t>Deadline: 17-Apr-2026 The American Psychological Foundation (APF) is inviting applications for the Walter Katkovsky Research Grant, supporting psychotherapy research. Two grants of $22,500 each are available to psychologists within 12 years postdoctoral, aiming to advance understanding of behavioral, emotional, or cognitive changes facilitated by psychotherapy. Overview of the Grant The Walter Katkovsky Research Grant Program</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Science and SciLifeLab Prize</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>all,</t>
-        </is>
-      </c>
+          <t>American Psychological Foundation</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>15-Jul-2026</t>
+          <t>17-Apr-2026</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3251,12 +3325,12 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://scienceprize.scilifelab.se/</t>
+          <t>https://ampsychfdn.org/funding/katkovsky-research/</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/research/call-for-entries-science-and-scilifelab-prize-for-young-scientists/</t>
+          <t>https://www2.fundsforngos.org/research/apply-now-for-walter-katkovsky-research-grant-program-united-states/</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3264,31 +3338,28 @@
           <t>https://www2.fundsforngos.org/tag/lebanon/</t>
         </is>
       </c>
+      <c r="J62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Call for Entries: Wellcome Early-Career Awards</t>
+          <t>Apply Now: Indo-French Joint Call for Research and Innovation</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Deadline: 21-Jul-2026 The Wellcome Early-Career Awards provide funding for early-career researchers across any discipline to establish themselves as independent investigators. Grants cover salary and up to £400,000 for research costs, enabling awardees to develop research maturity, transferable skills, and independent research programmes over a period of up to five years. Program Overview The Wellcome Early-Career</t>
+          <t>Deadline: 20-Apr-2026 The Department of Science and Technology (DST), India and the French National Research Agency (ANR), France are inviting joint research proposals to strengthen India–France collaboration in Applied Mathematics and Artificial Intelligence (AI). The call supports binational projects of up to three years in four priority areas, with up to €1.5 million allocated by</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Wellcome</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>is required</t>
-        </is>
-      </c>
+          <t>Department of Science and Technology</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>21-Jul-2026</t>
+          <t>20-Apr-2026</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3298,12 +3369,12 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://wellcome.org/research-funding/schemes/wellcome-early-career-awards</t>
+          <t>https://onlinedst.gov.in/Projectproposalformat.aspx?Id=2381</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/research/call-for-entries-wellcome-early-career-awards/</t>
+          <t>https://www2.fundsforngos.org/research/apply-now-indo-french-joint-call-for-research-and-innovation/</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3311,27 +3382,28 @@
           <t>https://www2.fundsforngos.org/tag/lebanon/</t>
         </is>
       </c>
+      <c r="J63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Call for Nominations: Abdul Hameed Shoman Award for Arab Researchers</t>
+          <t>Call for Applications: TWAS-CSIR Postgraduate Fellowship Programme</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Deadline: 31-Mar-2026 The Abdul Hameed Shoman Award supports and promotes high-impact scientific research in the Arab world, inspiring a new generation of Arab researchers. Winners receive $20,000 USD, a trophy, and a certificate, recognizing contributions across six major scientific fields with two topics announced annually per field. Overview The award aims to encourage high-quality research</t>
+          <t>Deadline: 06-May-2026 The TWAS-CSIR Postgraduate Fellowship supports foreign scholars from developing countries to pursue PhD research in emerging science and technology areas in India. The program offers Sandwich and Full-Time Fellowships, providing up to four years of funding at CSIR research laboratories and institutes to strengthen scientific capacity and doctoral research opportunities. Overview The fellowship</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Abdul Hameed Shoman Foundation</t>
+          <t>TWAS</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>31-Mar-2026</t>
+          <t>06-May-2026</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3341,12 +3413,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://shoman.org/en/ResearchersAward</t>
+          <t>https://twas.org/opportunity/twas-csir-postgraduate-fellowship-programme</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/research/call-for-nominations-abdul-hameed-shoman-award-for-arab-researchers/</t>
+          <t>https://www2.fundsforngos.org/research/call-for-applications-twas-csir-postgraduate-fellowship-programme/</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3354,27 +3426,32 @@
           <t>https://www2.fundsforngos.org/tag/lebanon/</t>
         </is>
       </c>
+      <c r="J64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Call for Research Proposals: Global DPI Insights Community Fund</t>
+          <t>Call for Entries: Science and SciLifeLab Prize for Young Scientists</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Deadline: 30-Apr-2026 The Center for Financial Inclusion’s Global DPI Insights Community Fund provides research grants of up to USD $50,000 to support studies on the design, implementation, and sustainability of digital public infrastructure (DPI) systems. Grants focus on locally grounded evidence, consumer protection, market competition, and inclusive financial systems. Program Overview The Global DPI Insights</t>
+          <t>Deadline: 15-Jul-2026 The SciLifeLab and Science Prize for Young Scientists honors exceptional doctoral research in life sciences, offering winners financial awards, global recognition, and publication opportunities. Each year, four category winners are selected, including a grand prize of USD 30,000, with category winners receiving USD 10,000 each. Winners also gain the chance to present their</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Center for Financial Inclusion</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr"/>
+          <t>Science and SciLifeLab Prize</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>all,</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>30-Apr-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3384,12 +3461,12 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.centerforfinancialinclusion.org/research/2026-call-for-research-proposals/</t>
+          <t>https://scienceprize.scilifelab.se/</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/research/call-for-research-proposals-global-dpi-insights-community-fund/</t>
+          <t>https://www2.fundsforngos.org/research/call-for-entries-science-and-scilifelab-prize-for-young-scientists/</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3397,31 +3474,32 @@
           <t>https://www2.fundsforngos.org/tag/lebanon/</t>
         </is>
       </c>
+      <c r="J65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Entries open for Falling Walls Lab Accra (Ghana)</t>
+          <t>Call for Entries: Wellcome Early-Career Awards</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Deadline: 04-May-2026 Falling Walls Lab Accra invites students and early-career professionals to present groundbreaking ideas that break barriers in science, technology, and society. The program emphasizes interdisciplinary innovation, social impact, and global knowledge exchange. Applicants must be at least 18 years old, meet academic criteria, submit individually in English, and participate in their closest Lab,</t>
+          <t>Deadline: 21-Jul-2026 The Wellcome Early-Career Awards provide funding for early-career researchers across any discipline to establish themselves as independent investigators. Grants cover salary and up to £400,000 for research costs, enabling awardees to develop research maturity, transferable skills, and independent research programmes over a period of up to five years. Program Overview The Wellcome Early-Career</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Falling Walls Foundation</t>
+          <t>Wellcome</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>to Falling Walls Lab Accra?</t>
+          <t>is required</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>04-May-2026</t>
+          <t>21-Jul-2026</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3431,12 +3509,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://falling-walls.com/falling-walls-lab-accra-ghana-daad</t>
+          <t>https://wellcome.org/research-funding/schemes/wellcome-early-career-awards</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/research/entries-open-for-falling-walls-lab-accra-ghana/</t>
+          <t>https://www2.fundsforngos.org/research/call-for-entries-wellcome-early-career-awards/</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3444,31 +3522,28 @@
           <t>https://www2.fundsforngos.org/tag/lebanon/</t>
         </is>
       </c>
+      <c r="J66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Falling Walls Lab Competition: Break Barriers, Shape the Future (Finland)</t>
+          <t>Call for Nominations: Abdul Hameed Shoman Award for Arab Researchers</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Deadline: 21-May-2026 Falling Walls Lab is an international platform for students and early-career professionals to present groundbreaking ideas that break barriers in science and society. The program emphasizes innovation, interdisciplinary collaboration, and early-stage solutions across diverse fields. Applicants must meet academic or professional criteria, submit individually in English, and participate in their closest Lab, with</t>
+          <t>Deadline: 31-Mar-2026 The Abdul Hameed Shoman Award supports and promotes high-impact scientific research in the Arab world, inspiring a new generation of Arab researchers. Winners receive $20,000 USD, a trophy, and a certificate, recognizing contributions across six major scientific fields with two topics announced annually per field. Overview The award aims to encourage high-quality research</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Falling Walls Foundation</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>to Falling Walls Lab?</t>
-        </is>
-      </c>
+          <t>Abdul Hameed Shoman Foundation</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>21-May-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3478,12 +3553,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://falling-walls.com/falling-walls-lab-eastern-finland</t>
+          <t>https://shoman.org/en/ResearchersAward</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/research/falling-walls-lab-competition-break-barriers-shape-the-future-finland/</t>
+          <t>https://www2.fundsforngos.org/research/call-for-nominations-abdul-hameed-shoman-award-for-arab-researchers/</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3491,27 +3566,32 @@
           <t>https://www2.fundsforngos.org/tag/lebanon/</t>
         </is>
       </c>
+      <c r="J67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Funding and Support for Negative Emissions Research Projects in Sweden</t>
+          <t>Post-Doctoral Study Grants for Early-Career Researchers</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Deadline: 31-Aug-2026 The Swedish Energy Agency Negative Emissions Grant 2026 under Industriklivet funds research and development projects focused on permanent negative emissions solutions. With a total budget of ~15 million SEK, the call supports projects involving carbon capture, transport, and geological storage of greenhouse gases. Eligible applicants include universities, research institutes, public sector bodies, and</t>
+          <t>Deadline: 31-Mar-2026 he Post-Doctoral Study Grants provide up to €45,000 per year for researchers to advance their careers through focused post-doctoral projects. Funding supports researchers in fields such as Ethology, Paleontology, Archaeology, Anthropology, Psychology, Epistemology, Logic, and Neuroscience, either in France or abroad. What Are the Post-Doctoral Study Grants? The Post-Doctoral Study Grants offer financial</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Energimyndigheten</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr"/>
+          <t>Fyssen Foundation</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>for the Post-Doctoral Study Grants?</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>31-Aug-2026</t>
+          <t>31-Mar-2026</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3521,12 +3601,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.energimyndigheten.se/utlysningar/stod-for-forskning-for-negativa-utslapp/</t>
+          <t>https://www.fondationfyssen.fr/en/our-actions/study-grants/</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/research/funding-and-support-for-negative-emissions-research-projects-in-sweden/</t>
+          <t>https://www2.fundsforngos.org/research/post-doctoral-study-grants-for-early-career-researchers/</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3534,31 +3614,32 @@
           <t>https://www2.fundsforngos.org/tag/lebanon/</t>
         </is>
       </c>
+      <c r="J68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Paired Early Career Fellowship in Applied Research (India and Germany)</t>
+          <t>Pre-Doctoral and Post-Doctoral Fellowship Grant Program</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Deadline: 31-Mar-2026 The Paired Early Career Fellowship in Applied Research (PECFAR), offered by the Indo-German Science and Technology Centre, supports early career researchers from India and Germany in collaborative STEM research. Fellows engage in short-term research visits, expand professional networks, and gain financial support for travel and living expenses. This initiative fosters cross-border innovation, institutional</t>
+          <t>Deadline: 08-Jun-2026 The Pre-Doctoral and Post-Doctoral Fellowship Grant Program provides up to $300,000 over three years to support researchers focused on DIPG (Diffuse Intrinsic Pontine Glioma). Fellowships fund research time, foster mentorship, and encourage publication and data sharing to advance understanding, treatment, and potential cures for this rare pediatric brain cancer. What is the Fellowship</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>IGSTC</t>
+          <t>ChadTough Defeat DIPG Foundation</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>for PECFAR?</t>
+          <t>Awards are made to the institution or lab, not directly to the fellow.</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>31-Mar-2026</t>
+          <t>08-Jun-2026</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3568,12 +3649,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.igstc.org/home/pecfar_current_call</t>
+          <t>https://chadtough.org/research/grant-application/</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/research/paired-early-career-fellowship-in-applied-research-india-and-germany/</t>
+          <t>https://www2.fundsforngos.org/research/pre-doctoral-and-post-doctoral-fellowship-grant-program/</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3581,31 +3662,28 @@
           <t>https://www2.fundsforngos.org/tag/lebanon/</t>
         </is>
       </c>
+      <c r="J69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Post-Doctoral Study Grants for Early-Career Researchers</t>
+          <t>Scholarships to Enhance and Empower the Development of Scientists (US)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Deadline: 31-Mar-2026 he Post-Doctoral Study Grants provide up to €45,000 per year for researchers to advance their careers through focused post-doctoral projects. Funding supports researchers in fields such as Ethology, Paleontology, Archaeology, Anthropology, Psychology, Epistemology, Logic, and Neuroscience, either in France or abroad. What Are the Post-Doctoral Study Grants? The Post-Doctoral Study Grants offer financial</t>
+          <t>Deadline: 03-Apr-2026 The American Psychological Foundation (APF) has announced the sixth annual SEEDS (Scholarships to Enhance and Empower the Development of Scientists) program, a mentoring and career-enhancement initiative for diverse early-career neuroscientists. The program is designed to help participants transition into and remain in academic positions, strengthen NSF and NIH grant applications, and receive long-term</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Fyssen Foundation</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>for the Post-Doctoral Study Grants?</t>
-        </is>
-      </c>
+          <t>American Psychological Foundation</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>31-Mar-2026</t>
+          <t>03-Apr-2026</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3615,12 +3693,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.fondationfyssen.fr/en/our-actions/study-grants/</t>
+          <t>https://ampsychfdn.org/funding/see-d/</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/research/post-doctoral-study-grants-for-early-career-researchers/</t>
+          <t>https://www2.fundsforngos.org/research/scholarships-to-enhance-and-empower-the-development-of-scientists-us/</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3628,31 +3706,32 @@
           <t>https://www2.fundsforngos.org/tag/lebanon/</t>
         </is>
       </c>
+      <c r="J70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Pre-Doctoral and Post-Doctoral Fellowship Grant Program</t>
+          <t>Apply Now: Gender Equality in HIV Policies and Programming Course</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Deadline: 08-Jun-2026 The Pre-Doctoral and Post-Doctoral Fellowship Grant Program provides up to $300,000 over three years to support researchers focused on DIPG (Diffuse Intrinsic Pontine Glioma). Fellowships fund research time, foster mentorship, and encourage publication and data sharing to advance understanding, treatment, and potential cures for this rare pediatric brain cancer. What is the Fellowship</t>
+          <t>Deadline: 31-Dec-2026 The Integrating Gender Equality in HIV Policies and Programming Course is a global learning programme designed to strengthen HIV responses by promoting gender equality and women’s empowerment. It provides practical tools to integrate gender into HIV policies, programmes, and interventions. The course is open worldwide and targets government, civil society, and health sector</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ChadTough Defeat DIPG Foundation</t>
+          <t>UN Women</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Awards are made to the institution or lab, not directly to the fellow.</t>
+          <t>anyone globally</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>31-Dec-2026</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3662,12 +3741,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://chadtough.org/research/grant-application/</t>
+          <t>https://portal.trainingcentre.unwomen.org/product/gender-equality-in-hiv-policy-and-programming/</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/research/pre-doctoral-and-post-doctoral-fellowship-grant-program/</t>
+          <t>https://www2.fundsforngos.org/women-gender/apply-now-gender-equality-in-hiv-policies-and-programming-course/</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3675,31 +3754,32 @@
           <t>https://www2.fundsforngos.org/tag/lebanon/</t>
         </is>
       </c>
+      <c r="J71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Apply Now: Gender Equality in HIV Policies and Programming Course</t>
+          <t>GTF Olympiad Grants Empowering STEM Talent Worldwide</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Deadline: 31-Dec-2026 The Integrating Gender Equality in HIV Policies and Programming Course is a global learning programme designed to strengthen HIV responses by promoting gender equality and women’s empowerment. It provides practical tools to integrate gender into HIV policies, programmes, and interventions. The course is open worldwide and targets government, civil society, and health sector</t>
+          <t>Deadline: 15-May-2026 The GTF Olympiad Grants 2026 support organizations worldwide to identify and nurture high-potential STEM students, especially through Olympiads and competitions. Grants range from $20,000 to $50,000, funding training camps, competitions, and talent development initiatives. The programme aims to strengthen the global STEM Olympiad ecosystem and empower the next generation of innovators. What are</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>UN Women</t>
+          <t>Global Talent Fund</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>anyone globally</t>
+          <t>Global (open worldwide)</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>31-Dec-2026</t>
+          <t>15-May-2026</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3709,12 +3789,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://portal.trainingcentre.unwomen.org/product/gender-equality-in-hiv-policy-and-programming/</t>
+          <t>https://www.globtalent.org/gtf-olympiad-grants</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/women-gender/apply-now-gender-equality-in-hiv-policies-and-programming-course/</t>
+          <t>https://www2.fundsforngos.org/youth-adolescents/gtf-olympiad-grants-empowering-stem-talent-worldwide/</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3722,31 +3802,28 @@
           <t>https://www2.fundsforngos.org/tag/lebanon/</t>
         </is>
       </c>
+      <c r="J72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>RFAs: Black Women Photographers x Nikon Grant Program</t>
+          <t>Open Call: Summer Company Program for Young Entrepreneurs (Canada)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Deadline: 22-Mar-2026 The Black Women Photographers x Nikon Grant Program provides quarterly grants to Black women photographers, combining $2,500 in funding with professional Nikon camera equipment to support creative development. Each quarter, one photographer receives financial assistance and a Nikon Z6III camera kit with a 24–70mm f/4 lens to help strengthen their photography practice. Overview</t>
+          <t>Deadline: 08-May-2026 The Summer Company Program 2026 is now open for applications and supports students in Ontario aged 15 to 29 who want to start and run a small business during the summer. Eligible participants can receive up to $3,000 in grant funding, along with business training, mentorship, and hands-on entrepreneurial experience. What is the</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Black Women Photographers</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Black women photographers and creators</t>
-        </is>
-      </c>
+          <t>City of Toronto</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>22-Mar-2026</t>
+          <t>08-May-2026</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3756,12 +3833,12 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://blackwomenphotographers.com/grant-fund</t>
+          <t>https://www.toronto.ca/business-economy/business-operation-growth/business-incentives/summer-company-grant/</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/women-gender/rfas-black-women-photographers-x-nikon-grant-program/</t>
+          <t>https://www2.fundsforngos.org/youth-adolescents/open-call-summer-company-program-for-young-entrepreneurs-canada/</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3769,31 +3846,32 @@
           <t>https://www2.fundsforngos.org/tag/lebanon/</t>
         </is>
       </c>
+      <c r="J73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>GTF Olympiad Grants Empowering STEM Talent Worldwide</t>
+          <t>Call for Proposals: Polish Development Aid Competition 2026 (Poland)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Deadline: 15-May-2026 The GTF Olympiad Grants 2026 support organizations worldwide to identify and nurture high-potential STEM students, especially through Olympiads and competitions. Grants range from $20,000 to $50,000, funding training camps, competitions, and talent development initiatives. The programme aims to strengthen the global STEM Olympiad ecosystem and empower the next generation of innovators. What are</t>
+          <t>Deadline: 09-Apr-2026 The Polish Development Aid 2026 competition, launched by the Polish Ministry of Foreign Affairs, funds international development projects focused on governance, health, education, entrepreneurship, and inequality reduction. It supports NGOs, academic institutions, and non-profits in selected countries with defined geographic priorities and exclusions. Funding ranges across regions including Ukraine, Moldova, Palestine, Lebanon, Kenya,</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Global Talent Fund</t>
+          <t>Minister of Foreign Affairs</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Global (open worldwide)</t>
+          <t>for Polish Development Aid 2026?</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>15-May-2026</t>
+          <t>09-Apr-2026</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3803,44 +3881,49 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.globtalent.org/gtf-olympiad-grants</t>
+          <t>https://www.gov.pl/web/dyplomacja/ogloszenie-konkursu-polska-pomoc-rozwojowa-2026</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/youth-adolescents/gtf-olympiad-grants-empowering-stem-talent-worldwide/</t>
+          <t>https://www2.fundsforngos.org/economic-development/call-for-proposals-polish-development-aid-competition-2026-poland/</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/tag/lebanon/</t>
+          <t>https://www2.fundsforngos.org/category/education/</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>The Polish Development Aid competition funds international development projects implemented by NGOs, academic institutions, and non-profits to improve governance, health, education, entrepreneurship, and reduce inequality for communities in selected priority countries.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Call for Proposals: Polish Development Aid Competition 2026 (Poland)</t>
+          <t>Applications open for Mediterranean Youth in Audiovisual Field</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Deadline: 09-Apr-2026 The Polish Development Aid 2026 competition, launched by the Polish Ministry of Foreign Affairs, funds international development projects focused on governance, health, education, entrepreneurship, and inequality reduction. It supports NGOs, academic institutions, and non-profits in selected countries with defined geographic priorities and exclusions. Funding ranges across regions including Ukraine, Moldova, Palestine, Lebanon, Kenya,</t>
+          <t>Deadline: 18-Mar-2026 The MED-Y.C.I Programme invites 200 young people (ages 18–30) from select Mediterranean regions to participate in a fully funded learning programme focused on audiovisual storytelling, digital creativity, and civic engagement. The initiative combines workshops, peer exchange, and hands-on experiences to strengthen creative, digital, and civic skills while fostering regional collaboration. Overview of the</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Minister of Foreign Affairs</t>
+          <t>Interreg</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>for Polish Development Aid 2026?</t>
+          <t>to MED-Y.C.I?</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>09-Apr-2026</t>
+          <t>18-Mar-2026</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3850,12 +3933,12 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.gov.pl/web/dyplomacja/ogloszenie-konkursu-polska-pomoc-rozwojowa-2026</t>
+          <t>https://www.interregnextmed.eu/medyci-launches-a-call-for-applications-for-mediterranean-young-people-in-audiovisual-field/</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/economic-development/call-for-proposals-polish-development-aid-competition-2026-poland/</t>
+          <t>https://www2.fundsforngos.org/education/applications-open-for-mediterranean-youth-in-audiovisual-field/</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3863,31 +3946,32 @@
           <t>https://www2.fundsforngos.org/category/education/</t>
         </is>
       </c>
+      <c r="J75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Applications open for Mediterranean Youth in Audiovisual Field</t>
+          <t>Climate-Resilient Agriculture and Emergency Response (Palestine)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Deadline: 18-Mar-2026 The MED-Y.C.I Programme invites 200 young people (ages 18–30) from select Mediterranean regions to participate in a fully funded learning programme focused on audiovisual storytelling, digital creativity, and civic engagement. The initiative combines workshops, peer exchange, and hands-on experiences to strengthen creative, digital, and civic skills while fostering regional collaboration. Overview of the</t>
+          <t>Deadline: 17-Mar-2026 The World Food Programme (WFP) seeks partners to implement climate-resilient agriculture and emergency response initiatives in the West Bank. The program focuses on improving local food production, strengthening livelihoods, supporting vulnerable households, and promoting nutrition-sensitive, climate-smart agricultural practices. Overview of the Initiative WFP is launching a program to enhance agricultural resilience and emergency</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Interreg</t>
+          <t>UN Partner Portal</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>to MED-Y.C.I?</t>
+          <t>Eligible organizations must:</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>18-Mar-2026</t>
+          <t>17-Mar-2026</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3897,44 +3981,45 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.interregnextmed.eu/medyci-launches-a-call-for-applications-for-mediterranean-young-people-in-audiovisual-field/</t>
+          <t>https://www.unpartnerportal.org/landing/opportunities/</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/education/applications-open-for-mediterranean-youth-in-audiovisual-field/</t>
+          <t>https://www2.fundsforngos.org/community-development/climate-resilient-agriculture-and-emergency-response-palestine/</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/category/education/</t>
+          <t>https://www2.fundsforngos.org/category/economic-development/</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>The World Food Programme seeks partners to improve local food production and strengthen livelihoods for vulnerable households in the West Bank through climate-resilient and nutrition-sensitive agricultural practices.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Climate-Resilient Agriculture and Emergency Response (Palestine)</t>
+          <t>AFRISE Challenge Empowers Young Entrepreneurs to Drive African Economic Growth</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Deadline: 17-Mar-2026 The World Food Programme (WFP) seeks partners to implement climate-resilient agriculture and emergency response initiatives in the West Bank. The program focuses on improving local food production, strengthening livelihoods, supporting vulnerable households, and promoting nutrition-sensitive, climate-smart agricultural practices. Overview of the Initiative WFP is launching a program to enhance agricultural resilience and emergency</t>
+          <t>Deadline: 27-Mar-2026 The AFRISE Challenge offers African youth entrepreneurs aged 18–35 a platform to scale innovative ventures across sectors such as healthcare, agriculture, energy, education, and fintech. Participants from select African countries receive mentorship, leadership development, and access to grant and equity funding, culminating in an International Demo Day. The program also provides over $600,000</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>UN Partner Portal</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Eligible organizations must:</t>
-        </is>
-      </c>
+          <t>Concordia University</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>17-Mar-2026</t>
+          <t>27-Mar-2026</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3944,12 +4029,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.unpartnerportal.org/landing/opportunities/</t>
+          <t>https://hindsightventures.co/flagship-programs/afrise-challenge-2026</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/community-development/climate-resilient-agriculture-and-emergency-response-palestine/</t>
+          <t>https://www2.fundsforngos.org/economic-development/afrise-challenge-empowers-young-entrepreneurs-to-drive-african-economic-growth/</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3957,27 +4042,32 @@
           <t>https://www2.fundsforngos.org/category/economic-development/</t>
         </is>
       </c>
+      <c r="J77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>AFRISE Challenge Empowers Young Entrepreneurs to Drive African Economic Growth</t>
+          <t>Applications open for Blue Economy and Green Sustainability Initiative – Lebanon</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Deadline: 27-Mar-2026 The AFRISE Challenge offers African youth entrepreneurs aged 18–35 a platform to scale innovative ventures across sectors such as healthcare, agriculture, energy, education, and fintech. Participants from select African countries receive mentorship, leadership development, and access to grant and equity funding, culminating in an International Demo Day. The program also provides over $600,000</t>
+          <t>Deadline: 03-Apr-2026 The European Commission is inviting grant applications to boost Lebanon’s blue economy and green sustainability through economic growth, climate resilience, and environmental conservation. Funding supports projects under two lots: Lot 1 focuses on sustainable fisheries, aquaculture, and blue economy SMEs; Lot 2 targets forest restoration, wildfire prevention, and ecosystem management. Grants range from</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Concordia University</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr"/>
+          <t>European Commission</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>per Lot:</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>27-Mar-2026</t>
+          <t>03-Apr-2026</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3987,12 +4077,12 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://hindsightventures.co/flagship-programs/afrise-challenge-2026</t>
+          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/prospect-details/184458PROSPECTSEN?isExactMatch=true&amp;status=31094502&amp;order=DESC&amp;pageNumber=1&amp;pageSize=50&amp;sortBy=startDate</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/economic-development/afrise-challenge-empowers-young-entrepreneurs-to-drive-african-economic-growth/</t>
+          <t>https://www2.fundsforngos.org/economic-development/applications-open-for-blue-economy-and-green-sustainability-initiative-lebanon/</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -4000,31 +4090,28 @@
           <t>https://www2.fundsforngos.org/category/economic-development/</t>
         </is>
       </c>
+      <c r="J78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Applications open for Blue Economy and Green Sustainability Initiative – Lebanon</t>
+          <t>Call for Income Improvement and Economic Inclusion Projects (Morocco)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Deadline: 03-Apr-2026 The European Commission is inviting grant applications to boost Lebanon’s blue economy and green sustainability through economic growth, climate resilience, and environmental conservation. Funding supports projects under two lots: Lot 1 focuses on sustainable fisheries, aquaculture, and blue economy SMEs; Lot 2 targets forest restoration, wildfire prevention, and ecosystem management. Grants range from</t>
+          <t>Deadline: 27-Feb-2026 The National Initiative for Human Development (INDH) – Phase III (2026) has launched a call for proposals in Taroudant Province, Morocco under the Income Improvement Axis. The program offers up to AED 200,000 per project, covering 90% of costs, to support cooperatives and youth or women’s economic groups that create sustainable employment and</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>European Commission</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>per Lot:</t>
-        </is>
-      </c>
+          <t>Regional Committee for Human Development in Taroudant Province</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>03-Apr-2026</t>
+          <t>27-Feb-2026</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -4034,12 +4121,12 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://ec.europa.eu/info/funding-tenders/opportunities/portal/screen/opportunities/prospect-details/184458PROSPECTSEN?isExactMatch=true&amp;status=31094502&amp;order=DESC&amp;pageNumber=1&amp;pageSize=50&amp;sortBy=startDate</t>
+          <t>https://www.maroc.ma/ar/%D8%A7%D9%84%D8%A3%D8%AE%D8%A8%D8%A7%D8%B1/%D8%A8%D8%B1%D9%86%D8%A7%D9%85%D8%AC-%D8%AA%D8%AD%D8%B3%D9%8A%D9%86-%D8%A7%D9%84%D8%AF%D8%AE%D9%84-%D9%88%D8%A7%D9%84%D8%A5%D8%AF%D9%85%D8%A7%D8%AC-%D8%A7%D9%84%D8%A7%D9%82%D8%AA%D8%B5%D8%A7%D8%AF%D9%8A-%D9%84%D9%84%D8%B4%D8%A8%D8%A7%D8%A8-%D8%A8%D8%AA%D8%A7%D8%B1%D9%88%D8%AF%D8%A7%D9%86%D8%AA-%D8%A7%D9%84%D8%A5%D8%B9%D9%84%D8%A7%D9%86-%D8%B9%D9%86-%D9%81%D8%AA%D8%AD-%D8%A8%D8%A7%D8%A8-%D8%AA%D9%82%D8%AF%D9%8A%D9%85-%D8%B7%D9%84%D8%A8%D8%A7%D8%AA-%D8%A7%D9%82%D8%AA%D8%B1%D8%A7%D8%AD-%D9%85%D8%B4%D8%A7%D8%B1%D9%8A%D8%B9</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/economic-development/applications-open-for-blue-economy-and-green-sustainability-initiative-lebanon/</t>
+          <t>https://www2.fundsforngos.org/economic-development/call-for-income-improvement-and-economic-inclusion-projects-morocco/</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -4047,27 +4134,32 @@
           <t>https://www2.fundsforngos.org/category/economic-development/</t>
         </is>
       </c>
+      <c r="J79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Call for Income Improvement and Economic Inclusion Projects (Morocco)</t>
+          <t>Fondation Nexans Call for Sustainable and Inclusive Energy Projects</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Deadline: 27-Feb-2026 The National Initiative for Human Development (INDH) – Phase III (2026) has launched a call for proposals in Taroudant Province, Morocco under the Income Improvement Axis. The program offers up to AED 200,000 per project, covering 90% of costs, to support cooperatives and youth or women’s economic groups that create sustainable employment and</t>
+          <t>Deadline: 02-Mar-2026 The Fondation Nexans provides grants ranging from €10,000 to €40,000 to international NGOs and associations implementing renewable energy and sustainable electrification projects. The program supports access to energy for underserved communities, technical education, and environmental sustainability initiatives aligned with at least three UN Sustainable Development Goals (SDGs). Priority is given to countries where</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Regional Committee for Human Development in Taroudant Province</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
+          <t>Fondation Nexans</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>are prioritized where Nexans operates, including:</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>27-Feb-2026</t>
+          <t>02-Mar-2026</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -4077,12 +4169,12 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.maroc.ma/ar/%D8%A7%D9%84%D8%A3%D8%AE%D8%A8%D8%A7%D8%B1/%D8%A8%D8%B1%D9%86%D8%A7%D9%85%D8%AC-%D8%AA%D8%AD%D8%B3%D9%8A%D9%86-%D8%A7%D9%84%D8%AF%D8%AE%D9%84-%D9%88%D8%A7%D9%84%D8%A5%D8%AF%D9%85%D8%A7%D8%AC-%D8%A7%D9%84%D8%A7%D9%82%D8%AA%D8%B5%D8%A7%D8%AF%D9%8A-%D9%84%D9%84%D8%B4%D8%A8%D8%A7%D8%A8-%D8%A8%D8%AA%D8%A7%D8%B1%D9%88%D8%AF%D8%A7%D9%86%D8%AA-%D8%A7%D9%84%D8%A5%D8%B9%D9%84%D8%A7%D9%86-%D8%B9%D9%86-%D9%81%D8%AA%D8%AD-%D8%A8%D8%A7%D8%A8-%D8%AA%D9%82%D8%AF%D9%8A%D9%85-%D8%B7%D9%84%D8%A8%D8%A7%D8%AA-%D8%A7%D9%82%D8%AA%D8%B1%D8%A7%D8%AD-%D9%85%D8%B4%D8%A7%D8%B1%D9%8A%D8%B9</t>
+          <t>https://fondation.nexans.com/en/Call-for-Projects.html</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/economic-development/call-for-income-improvement-and-economic-inclusion-projects-morocco/</t>
+          <t>https://www2.fundsforngos.org/economic-development/fondation-nexans-call-for-sustainable-and-inclusive-energy-projects/</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4090,31 +4182,32 @@
           <t>https://www2.fundsforngos.org/category/economic-development/</t>
         </is>
       </c>
+      <c r="J80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Fondation Nexans Call for Sustainable and Inclusive Energy Projects</t>
+          <t>DWF Foundation Grants for Community Impact</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Deadline: 02-Mar-2026 The Fondation Nexans provides grants ranging from €10,000 to €40,000 to international NGOs and associations implementing renewable energy and sustainable electrification projects. The program supports access to energy for underserved communities, technical education, and environmental sustainability initiatives aligned with at least three UN Sustainable Development Goals (SDGs). Priority is given to countries where</t>
+          <t>Deadline: 30-Jun-2026 The DWF Foundation provides grants to registered charities that help individuals, groups, and communities reach their full potential. Funding supports projects in homelessness, health and wellbeing, employability, education, and environment and sustainability, with most grants under £5,000. Eligible organizations must operate in countries where DWF has a presence, including the UK, US, Canada,</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Fondation Nexans</t>
+          <t>DWF Foundation</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>are prioritized where Nexans operates, including:</t>
+          <t>Australia, Canada, France, Germany, India, Ireland, Italy, Poland, Qatar, Spain,</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>02-Mar-2026</t>
+          <t>30-Jun-2026</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -4124,40 +4217,41 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://fondation.nexans.com/en/Call-for-Projects.html</t>
+          <t>https://dwfgroup.com/en/about-us/dwf-foundation</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/economic-development/fondation-nexans-call-for-sustainable-and-inclusive-energy-projects/</t>
+          <t>https://www2.fundsforngos.org/environment/dwf-foundation-grants-for-community-impact/</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/category/economic-development/</t>
-        </is>
-      </c>
+          <t>https://www2.fundsforngos.org/category/employment-labor/</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>UNDP Launches Labour-Intensive Short-Term Employment Initiative – Lebanon</t>
+          <t>Open Call: Women in Agriculture Leadership Fellowship Program</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Deadline: 16-Mar-2026 The United Nations Development Programme (UNDP) has launched a Labour-Intensive Short-Term Employment initiative in Tyre and Marjaayoun districts under the Stabilization in Southern Lebanon Project. The initiative provides immediate income support to vulnerable returnees and host communities while rehabilitating infrastructure and restoring public spaces. The intervention has a total budget of USD 190,000</t>
+          <t>Deadline: 26-Apr-2026 The Women in Agriculture Leadership Program Fellowship empowers African women scientists in agriculture and climate resilience through a two-year, non-residential program. Fellows receive leadership training, mentoring, technical skills development, networking opportunities, and support for gender-responsive, climate-resilient agrifood research. About the Fellowship The Women in Agriculture Leadership Program Fellowship is designed to support African</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>UNDP</t>
+          <t>AWARD</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>16-Mar-2026</t>
+          <t>26-Apr-2026</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -4167,109 +4261,20 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://procurement-notices.undp.org/view_negotiation.cfm?nego_id=43112</t>
+          <t>https://awardfellowships.org/news/call-to-apply-for-the-women-in-agriculture-leadership-program-fellowship-for-the-africa-australia-partnership-for-climate-responsive-agriculture/</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/community-development/undp-launches-labour-intensive-short-term-employment-initiative-lebanon/</t>
+          <t>https://fundsforindividuals.fundsforngos.org/fellowships/open-call-women-in-agriculture-leadership-fellowship-program/</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>https://www2.fundsforngos.org/category/employment-labor/</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>DWF Foundation Grants for Community Impact</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Deadline: 30-Jun-2026 The DWF Foundation provides grants to registered charities that help individuals, groups, and communities reach their full potential. Funding supports projects in homelessness, health and wellbeing, employability, education, and environment and sustainability, with most grants under £5,000. Eligible organizations must operate in countries where DWF has a presence, including the UK, US, Canada,</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>DWF Foundation</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>Australia, Canada, France, Germany, India, Ireland, Italy, Poland, Qatar, Spain,</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>30-Jun-2026</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>view grant link</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://dwfgroup.com/en/about-us/dwf-foundation</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>https://www2.fundsforngos.org/environment/dwf-foundation-grants-for-community-impact/</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>https://www2.fundsforngos.org/category/employment-labor/</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Open Call: Women in Agriculture Leadership Fellowship Program</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Deadline: 26-Apr-2026 The Women in Agriculture Leadership Program Fellowship empowers African women scientists in agriculture and climate resilience through a two-year, non-residential program. Fellows receive leadership training, mentoring, technical skills development, networking opportunities, and support for gender-responsive, climate-resilient agrifood research. About the Fellowship The Women in Agriculture Leadership Program Fellowship is designed to support African</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>AWARD</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>26-Apr-2026</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>view grant link</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://awardfellowships.org/news/call-to-apply-for-the-women-in-agriculture-leadership-program-fellowship-for-the-africa-australia-partnership-for-climate-responsive-agriculture/</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>https://fundsforindividuals.fundsforngos.org/fellowships/open-call-women-in-agriculture-leadership-fellowship-program/</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
           <t>https://fundsforindividuals.fundsforngos.org/type_of_individuals/students/</t>
         </is>
       </c>
+      <c r="J82" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
